--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DF0A3E-E823-4D9F-8CFB-91C29FB389B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A4A370-67A0-41B3-A665-5A9304342CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="323">
   <si>
     <t>0</t>
   </si>
@@ -561,12 +561,6 @@
   </si>
   <si>
     <t>港</t>
-  </si>
-  <si>
-    <t>阵</t>
-  </si>
-  <si>
-    <t>砦</t>
   </si>
   <si>
     <t>城塞</t>
@@ -1193,6 +1187,26 @@
   </si>
   <si>
     <t>4846-6/4846-6_30</t>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopDefence", value:15, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-50, bound:2, tartgetType:0} ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopDefence", value:20, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-60, bound:2, tartgetType:0} ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopDefence", value:10, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-40, bound:2, tartgetType:0} ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1695,36 +1709,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AN120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.44140625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.5" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.21875" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="71.88671875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="37.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.88671875" style="2" customWidth="1"/>
-    <col min="36" max="36" width="37.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="102.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="71.875" style="2" customWidth="1"/>
+    <col min="33" max="33" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.875" style="2" customWidth="1"/>
+    <col min="36" max="36" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="164.75" style="2" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1744,10 +1758,10 @@
         <v>142</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>51</v>
@@ -1768,22 +1782,22 @@
         <v>54</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>104</v>
@@ -1798,22 +1812,22 @@
         <v>102</v>
       </c>
       <c r="AA1" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AB1" s="18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AC1" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AF1" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG1" s="9" t="s">
         <v>53</v>
@@ -1832,7 +1846,7 @@
       <c r="AM1" s="9"/>
       <c r="AN1" s="7"/>
     </row>
-    <row r="2" spans="1:40" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1876,7 +1890,7 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
     </row>
-    <row r="3" spans="1:40" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1887,7 +1901,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>109</v>
@@ -1900,10 +1914,10 @@
         <v>141</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>113</v>
@@ -1924,28 +1938,28 @@
         <v>55</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>111</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>116</v>
@@ -1957,19 +1971,19 @@
         <v>112</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AE3" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG3" s="13" t="s">
         <v>107</v>
@@ -1978,19 +1992,19 @@
         <v>106</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AJ3" s="13" t="s">
         <v>129</v>
       </c>
       <c r="AK3" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AL3" s="8"/>
       <c r="AM3" s="8"/>
       <c r="AN3" s="8"/>
     </row>
-    <row r="4" spans="1:40" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2016,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J4" s="15" t="s">
         <v>8</v>
@@ -2052,16 +2066,16 @@
         <v>8</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2073,7 +2087,7 @@
         <v>108</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AC4" s="15" t="s">
         <v>8</v>
@@ -2100,10 +2114,10 @@
         <v>5</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2133,10 +2147,10 @@
         <v>125</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>122</v>
@@ -2179,7 +2193,7 @@
       <c r="AG5" s="4"/>
       <c r="AM5" s="4"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2210,10 +2224,10 @@
         <v>126</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>124</v>
@@ -2256,7 +2270,7 @@
       <c r="AG6" s="4"/>
       <c r="AM6" s="4"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -2286,10 +2300,10 @@
         <v>126</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>123</v>
@@ -2326,18 +2340,21 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
       <c r="AM7" s="4"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>321</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2362,16 +2379,18 @@
         <v>133</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
+      <c r="Q8" s="6">
+        <v>1</v>
+      </c>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6">
@@ -2402,25 +2421,28 @@
       </c>
       <c r="AF8" s="4"/>
       <c r="AG8" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AH8" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="AM8" s="4"/>
     </row>
-    <row r="9" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2445,16 +2467,18 @@
         <v>134</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="6">
+        <v>1</v>
+      </c>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
       <c r="T9" s="6">
@@ -2481,29 +2505,32 @@
         <v>0</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AH9" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="AM9" s="4"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2528,10 +2555,10 @@
         <v>126</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>122</v>
@@ -2570,25 +2597,28 @@
       </c>
       <c r="AF10" s="4"/>
       <c r="AG10" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AH10" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
+      </c>
+      <c r="AK10" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="AM10" s="4"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2655,20 +2685,20 @@
       </c>
       <c r="AF11" s="4"/>
       <c r="AG11" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AM11" s="4"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2740,25 +2770,25 @@
       </c>
       <c r="AF12" s="4"/>
       <c r="AG12" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AM12" s="4"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D13" s="4">
         <v>2</v>
@@ -2821,11 +2851,11 @@
       </c>
       <c r="AF13" s="4"/>
       <c r="AG13" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AM13" s="4"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2893,11 +2923,11 @@
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AM14" s="4"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2969,11 +2999,11 @@
       </c>
       <c r="AF15" s="4"/>
       <c r="AG15" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AM15" s="4"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3045,11 +3075,11 @@
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AM16" s="4"/>
     </row>
-    <row r="17" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3121,11 +3151,11 @@
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AM17" s="4"/>
     </row>
-    <row r="18" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3197,16 +3227,16 @@
       </c>
       <c r="AF18" s="4"/>
       <c r="AG18" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AM18" s="4"/>
     </row>
-    <row r="19" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -3269,7 +3299,7 @@
       <c r="AG19" s="4"/>
       <c r="AM19" s="4"/>
     </row>
-    <row r="20" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3337,12 +3367,12 @@
       <c r="AG20" s="4"/>
       <c r="AM20" s="4"/>
     </row>
-    <row r="21" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D21" s="4">
         <v>3</v>
@@ -3405,16 +3435,16 @@
       </c>
       <c r="AF21" s="4"/>
       <c r="AG21" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AM21" s="4"/>
     </row>
-    <row r="22" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -3477,11 +3507,11 @@
       </c>
       <c r="AF22" s="4"/>
       <c r="AG22" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AM22" s="4"/>
     </row>
-    <row r="23" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3549,11 +3579,11 @@
       </c>
       <c r="AF23" s="4"/>
       <c r="AG23" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM23" s="4"/>
     </row>
-    <row r="24" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3621,11 +3651,11 @@
       </c>
       <c r="AF24" s="4"/>
       <c r="AG24" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM24" s="4"/>
     </row>
-    <row r="25" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3693,11 +3723,11 @@
       </c>
       <c r="AF25" s="4"/>
       <c r="AG25" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AM25" s="4"/>
     </row>
-    <row r="26" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3765,16 +3795,16 @@
       </c>
       <c r="AF26" s="4"/>
       <c r="AG26" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AM26" s="4"/>
     </row>
-    <row r="27" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
@@ -3837,11 +3867,11 @@
       </c>
       <c r="AF27" s="4"/>
       <c r="AG27" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AM27" s="4"/>
     </row>
-    <row r="28" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3909,7 +3939,7 @@
       <c r="AG28" s="4"/>
       <c r="AM28" s="4"/>
     </row>
-    <row r="29" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3977,7 +4007,7 @@
       <c r="AG29" s="4"/>
       <c r="AM29" s="4"/>
     </row>
-    <row r="30" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4043,7 +4073,7 @@
       <c r="AG30" s="4"/>
       <c r="AM30" s="4"/>
     </row>
-    <row r="31" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4111,7 +4141,7 @@
       <c r="AG31" s="4"/>
       <c r="AM31" s="4"/>
     </row>
-    <row r="32" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4177,7 +4207,7 @@
       <c r="AG32" s="4"/>
       <c r="AM32" s="4"/>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4245,7 +4275,7 @@
       <c r="AG33" s="4"/>
       <c r="AM33" s="4"/>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4313,7 +4343,7 @@
       <c r="AG34" s="4"/>
       <c r="AM34" s="4"/>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4380,19 +4410,19 @@
         <v>85</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AM35" s="4"/>
     </row>
-    <row r="36" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B36" s="4">
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4462,28 +4492,28 @@
         <v>86</v>
       </c>
       <c r="AF36" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG36" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AH36" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AG36" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AH36" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="AI36" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AM36" s="4"/>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B37" s="4">
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4553,28 +4583,28 @@
         <v>87</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AM37" s="4"/>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B38" s="4">
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4583,7 +4613,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H38" s="4">
         <v>1</v>
@@ -4607,22 +4637,22 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4645,27 +4675,27 @@
         <v>88</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B39" s="4">
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -4674,7 +4704,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H39" s="4">
         <v>1</v>
@@ -4698,22 +4728,22 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q39" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -4736,27 +4766,27 @@
         <v>89</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B40" s="4">
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -4765,7 +4795,7 @@
         <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H40" s="4">
         <v>1</v>
@@ -4789,22 +4819,22 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -4827,27 +4857,27 @@
         <v>90</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B41" s="4">
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -4856,7 +4886,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H41" s="4">
         <v>1</v>
@@ -4880,22 +4910,22 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -4918,27 +4948,27 @@
         <v>91</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B42" s="4">
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -4947,7 +4977,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H42" s="4">
         <v>1</v>
@@ -4971,22 +5001,22 @@
         <v>0</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5009,22 +5039,22 @@
         <v>92</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5059,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>121</v>
@@ -5091,30 +5121,30 @@
         <v>93</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B44" s="4">
         <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D44" s="4">
         <v>4</v>
@@ -5144,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>121</v>
@@ -5176,25 +5206,25 @@
         <v>94</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AK44" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5229,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>121</v>
@@ -5258,30 +5288,30 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B46" s="4">
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5311,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>121</v>
@@ -5326,10 +5356,10 @@
         <v>138</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5349,25 +5379,25 @@
         <v>1</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5402,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>121</v>
@@ -5414,7 +5444,7 @@
         <v>138</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -5434,25 +5464,25 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5487,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>121</v>
@@ -5519,22 +5549,22 @@
         <v>95</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="49" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -5569,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>121</v>
@@ -5601,27 +5631,27 @@
         <v>96</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B50" s="4">
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D50" s="4">
         <v>4</v>
@@ -5651,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>121</v>
@@ -5663,10 +5693,10 @@
         <v>138</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -5686,25 +5716,25 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="51" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="51" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -5739,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>121</v>
@@ -5774,22 +5804,22 @@
         <v>97</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="52" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -5824,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>121</v>
@@ -5859,22 +5889,22 @@
         <v>98</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="53" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -5909,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>121</v>
@@ -5942,19 +5972,19 @@
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="54" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -5989,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>121</v>
@@ -6024,25 +6054,25 @@
         <v>100</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AK54" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="55" spans="2:37" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="55" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6056,7 +6086,7 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H55" s="4">
         <v>2</v>
@@ -6080,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>121</v>
@@ -6113,19 +6143,19 @@
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="56" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6160,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>121</v>
@@ -6193,19 +6223,19 @@
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="57" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6219,7 +6249,7 @@
         <v>33</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H57" s="4">
         <v>2</v>
@@ -6243,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>121</v>
@@ -6276,19 +6306,19 @@
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="58" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6323,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>121</v>
@@ -6356,19 +6386,19 @@
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="59" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6382,7 +6412,7 @@
         <v>34</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H59" s="4">
         <v>2</v>
@@ -6406,22 +6436,22 @@
         <v>0</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6445,19 +6475,19 @@
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH59" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="60" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6492,22 +6522,22 @@
         <v>0</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q60" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6531,19 +6561,19 @@
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH60" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="61" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -6557,7 +6587,7 @@
         <v>35</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H61" s="4">
         <v>2</v>
@@ -6581,22 +6611,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6620,19 +6650,19 @@
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AH61" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI61" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AI61" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="AJ61" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="62" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -6667,22 +6697,22 @@
         <v>0</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -6706,19 +6736,19 @@
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AH62" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI62" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AI62" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="AJ62" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="63" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -6756,22 +6786,22 @@
         <v>0</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -6796,19 +6826,19 @@
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AH63" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AI63" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ63" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="64" spans="2:37" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="64" spans="2:37" x14ac:dyDescent="0.15">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -6844,22 +6874,22 @@
         <v>0</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q64" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -6884,24 +6914,24 @@
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AH64" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AI64" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ64" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="65" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B65" s="4">
         <v>61</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D65" s="4">
         <v>4</v>
@@ -6910,7 +6940,7 @@
         <v>37</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H65" s="4">
         <v>2</v>
@@ -6934,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>138</v>
@@ -6943,13 +6973,13 @@
         <v>134</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -6973,24 +7003,24 @@
       </c>
       <c r="AF65" s="4"/>
       <c r="AG65" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AH65" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="66" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B66" s="4">
         <v>62</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D66" s="4">
         <v>4</v>
@@ -7020,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>138</v>
@@ -7029,13 +7059,13 @@
         <v>126</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7059,24 +7089,24 @@
       </c>
       <c r="AF66" s="4"/>
       <c r="AG66" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AH66" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ66" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B67" s="4">
         <v>63</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D67" s="4">
         <v>4</v>
@@ -7085,7 +7115,7 @@
         <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H67" s="4">
         <v>2</v>
@@ -7109,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>138</v>
@@ -7118,13 +7148,13 @@
         <v>134</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7148,24 +7178,24 @@
       </c>
       <c r="AF67" s="4"/>
       <c r="AG67" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AH67" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="68" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B68" s="4">
         <v>64</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D68" s="4">
         <v>4</v>
@@ -7195,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>138</v>
@@ -7204,13 +7234,13 @@
         <v>126</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7234,19 +7264,19 @@
       </c>
       <c r="AF68" s="4"/>
       <c r="AG68" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AH68" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ68" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7262,7 +7292,7 @@
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7287,7 +7317,7 @@
       <c r="AF70" s="4"/>
       <c r="AM70" s="4"/>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7309,7 +7339,7 @@
       <c r="AF71" s="4"/>
       <c r="AM71" s="4"/>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7331,7 +7361,7 @@
       <c r="AF72" s="4"/>
       <c r="AM72" s="4"/>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7353,7 +7383,7 @@
       <c r="AF73" s="4"/>
       <c r="AM73" s="4"/>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7375,7 +7405,7 @@
       <c r="AF74" s="4"/>
       <c r="AM74" s="4"/>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7397,7 +7427,7 @@
       <c r="AF75" s="4"/>
       <c r="AM75" s="4"/>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7419,7 +7449,7 @@
       <c r="AF76" s="4"/>
       <c r="AM76" s="4"/>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7441,7 +7471,7 @@
       <c r="AF77" s="4"/>
       <c r="AM77" s="4"/>
     </row>
-    <row r="78" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7463,7 +7493,7 @@
       <c r="AF78" s="4"/>
       <c r="AM78" s="4"/>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7485,7 +7515,7 @@
       <c r="AF79" s="4"/>
       <c r="AM79" s="4"/>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7507,7 +7537,7 @@
       <c r="AF80" s="4"/>
       <c r="AM80" s="4"/>
     </row>
-    <row r="81" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7529,7 +7559,7 @@
       <c r="AF81" s="4"/>
       <c r="AM81" s="4"/>
     </row>
-    <row r="82" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7551,7 +7581,7 @@
       <c r="AF82" s="4"/>
       <c r="AM82" s="4"/>
     </row>
-    <row r="83" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7573,7 +7603,7 @@
       <c r="AF83" s="4"/>
       <c r="AM83" s="4"/>
     </row>
-    <row r="84" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -7595,7 +7625,7 @@
       <c r="AF84" s="4"/>
       <c r="AM84" s="4"/>
     </row>
-    <row r="85" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -7617,7 +7647,7 @@
       <c r="AF85" s="4"/>
       <c r="AM85" s="4"/>
     </row>
-    <row r="86" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -7639,7 +7669,7 @@
       <c r="AF86" s="4"/>
       <c r="AM86" s="4"/>
     </row>
-    <row r="87" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -7661,7 +7691,7 @@
       <c r="AF87" s="4"/>
       <c r="AM87" s="4"/>
     </row>
-    <row r="88" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -7683,7 +7713,7 @@
       <c r="AF88" s="4"/>
       <c r="AM88" s="4"/>
     </row>
-    <row r="89" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -7705,7 +7735,7 @@
       <c r="AF89" s="4"/>
       <c r="AM89" s="4"/>
     </row>
-    <row r="90" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -7727,7 +7757,7 @@
       <c r="AF90" s="4"/>
       <c r="AM90" s="4"/>
     </row>
-    <row r="91" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -7749,7 +7779,7 @@
       <c r="AF91" s="4"/>
       <c r="AM91" s="4"/>
     </row>
-    <row r="92" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -7771,7 +7801,7 @@
       <c r="AF92" s="4"/>
       <c r="AM92" s="4"/>
     </row>
-    <row r="93" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:39" x14ac:dyDescent="0.15">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -7784,7 +7814,7 @@
       <c r="AF93" s="4"/>
       <c r="AM93" s="4"/>
     </row>
-    <row r="94" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:39" x14ac:dyDescent="0.15">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -7803,7 +7833,7 @@
       <c r="AF94" s="4"/>
       <c r="AM94" s="4"/>
     </row>
-    <row r="95" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:39" x14ac:dyDescent="0.15">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -7822,7 +7852,7 @@
       <c r="AF95" s="4"/>
       <c r="AM95" s="4"/>
     </row>
-    <row r="96" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:39" x14ac:dyDescent="0.15">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -7841,7 +7871,7 @@
       <c r="AF96" s="4"/>
       <c r="AM96" s="4"/>
     </row>
-    <row r="97" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -7860,7 +7890,7 @@
       <c r="AF97" s="4"/>
       <c r="AM97" s="4"/>
     </row>
-    <row r="98" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -7879,7 +7909,7 @@
       <c r="AF98" s="4"/>
       <c r="AM98" s="4"/>
     </row>
-    <row r="99" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -7898,7 +7928,7 @@
       <c r="AF99" s="4"/>
       <c r="AM99" s="4"/>
     </row>
-    <row r="100" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -7917,7 +7947,7 @@
       <c r="AF100" s="4"/>
       <c r="AM100" s="4"/>
     </row>
-    <row r="101" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -7936,7 +7966,7 @@
       <c r="AF101" s="4"/>
       <c r="AM101" s="4"/>
     </row>
-    <row r="102" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -7955,7 +7985,7 @@
       <c r="AF102" s="4"/>
       <c r="AM102" s="4"/>
     </row>
-    <row r="103" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -7966,7 +7996,7 @@
       <c r="AE103" s="4"/>
       <c r="AF103" s="4"/>
     </row>
-    <row r="104" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -7977,7 +8007,7 @@
       <c r="AE104" s="4"/>
       <c r="AF104" s="4"/>
     </row>
-    <row r="105" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -7988,7 +8018,7 @@
       <c r="AE105" s="4"/>
       <c r="AF105" s="4"/>
     </row>
-    <row r="106" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -7999,7 +8029,7 @@
       <c r="AE106" s="4"/>
       <c r="AF106" s="4"/>
     </row>
-    <row r="107" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -8010,7 +8040,7 @@
       <c r="AE107" s="4"/>
       <c r="AF107" s="4"/>
     </row>
-    <row r="108" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8021,7 +8051,7 @@
       <c r="AE108" s="4"/>
       <c r="AF108" s="4"/>
     </row>
-    <row r="109" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8032,7 +8062,7 @@
       <c r="AE109" s="4"/>
       <c r="AF109" s="4"/>
     </row>
-    <row r="110" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8043,7 +8073,7 @@
       <c r="AE110" s="4"/>
       <c r="AF110" s="4"/>
     </row>
-    <row r="111" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8054,7 +8084,7 @@
       <c r="AE111" s="4"/>
       <c r="AF111" s="4"/>
     </row>
-    <row r="112" spans="5:39" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:39" x14ac:dyDescent="0.15">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8065,7 +8095,7 @@
       <c r="AE112" s="4"/>
       <c r="AF112" s="4"/>
     </row>
-    <row r="113" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8076,7 +8106,7 @@
       <c r="AE113" s="4"/>
       <c r="AF113" s="4"/>
     </row>
-    <row r="114" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8087,7 +8117,7 @@
       <c r="AE114" s="4"/>
       <c r="AF114" s="4"/>
     </row>
-    <row r="115" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8098,7 +8128,7 @@
       <c r="AE115" s="4"/>
       <c r="AF115" s="4"/>
     </row>
-    <row r="116" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8109,7 +8139,7 @@
       <c r="AE116" s="4"/>
       <c r="AF116" s="4"/>
     </row>
-    <row r="117" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8120,7 +8150,7 @@
       <c r="AE117" s="4"/>
       <c r="AF117" s="4"/>
     </row>
-    <row r="118" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8131,7 +8161,7 @@
       <c r="AE118" s="4"/>
       <c r="AF118" s="4"/>
     </row>
-    <row r="119" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8142,7 +8172,7 @@
       <c r="AE119" s="4"/>
       <c r="AF119" s="4"/>
     </row>
-    <row r="120" spans="5:32" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:32" x14ac:dyDescent="0.15">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A4A370-67A0-41B3-A665-5A9304342CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0EFED7-06AD-4594-8427-6C7DB78EF258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -773,9 +773,6 @@
     <t>Assets/Model/Prefab/4695.prefab</t>
   </si>
   <si>
-    <t>Assets/Model/Prefab/4697.prefab</t>
-  </si>
-  <si>
     <t>Assets/Model/Prefab/4699.prefab</t>
   </si>
   <si>
@@ -1168,44 +1165,53 @@
     <t>4846-6/4846-6_23</t>
   </si>
   <si>
+    <t>4846-6/4846-6_26</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_30</t>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopDefence", value:15, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-50, bound:2, tartgetType:0} ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopDefence", value:20, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-60, bound:2, tartgetType:0} ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopDefence", value:10, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-40, bound:2, tartgetType:0} ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>4846-6/4846-6_24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4697.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4846-6/4846-6_25</t>
-  </si>
-  <si>
-    <t>4846-6/4846-6_26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4846-6/4846-6_29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4846-6/4846-6_27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4846-6/4846-6_28</t>
-  </si>
-  <si>
-    <t>4846-6/4846-6_29</t>
-  </si>
-  <si>
-    <t>4846-6/4846-6_30</t>
-  </si>
-  <si>
-    <t>[{class:"BuildingImproveTroopDefence", value:15, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-50, bound:2, tartgetType:0} ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"BuildingImproveTroopDefence", value:20, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-60, bound:2, tartgetType:0} ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"BuildingImproveTroopDefence", value:10, bound:2, tartgetType:0},{class:"BuildingImproveTroopFoodCost", value:-40, bound:2, tartgetType:0} ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>砦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1758,10 +1764,10 @@
         <v>142</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>51</v>
@@ -1782,22 +1788,22 @@
         <v>54</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>104</v>
@@ -1821,7 +1827,7 @@
         <v>161</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
@@ -1914,10 +1920,10 @@
         <v>141</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>113</v>
@@ -1938,28 +1944,28 @@
         <v>55</v>
       </c>
       <c r="Q3" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="U3" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="R3" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>239</v>
-      </c>
       <c r="V3" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>111</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>116</v>
@@ -1977,7 +1983,7 @@
         <v>184</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE3" s="8" t="s">
         <v>57</v>
@@ -1992,13 +1998,13 @@
         <v>106</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AJ3" s="13" t="s">
         <v>129</v>
       </c>
       <c r="AK3" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AL3" s="8"/>
       <c r="AM3" s="8"/>
@@ -2030,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J4" s="15" t="s">
         <v>8</v>
@@ -2066,16 +2072,16 @@
         <v>8</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2114,7 +2120,7 @@
         <v>5</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.15">
@@ -2147,10 +2153,10 @@
         <v>125</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>122</v>
@@ -2224,10 +2230,10 @@
         <v>126</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>124</v>
@@ -2300,10 +2306,10 @@
         <v>126</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>123</v>
@@ -2354,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2379,7 +2385,7 @@
         <v>133</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>121</v>
@@ -2421,19 +2427,19 @@
       </c>
       <c r="AF8" s="4"/>
       <c r="AG8" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AH8" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AM8" s="4"/>
     </row>
@@ -2442,7 +2448,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2467,7 +2473,7 @@
         <v>134</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>121</v>
@@ -2509,19 +2515,19 @@
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH9" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AM9" s="4"/>
     </row>
@@ -2555,7 +2561,7 @@
         <v>126</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>121</v>
@@ -2597,19 +2603,19 @@
       </c>
       <c r="AF10" s="4"/>
       <c r="AG10" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AH10" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AM10" s="4"/>
     </row>
@@ -2685,16 +2691,16 @@
       </c>
       <c r="AF11" s="4"/>
       <c r="AG11" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH11" s="2" t="s">
         <v>186</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AM11" s="4"/>
     </row>
@@ -2770,16 +2776,16 @@
       </c>
       <c r="AF12" s="4"/>
       <c r="AG12" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AM12" s="4"/>
     </row>
@@ -2851,7 +2857,7 @@
       </c>
       <c r="AF13" s="4"/>
       <c r="AG13" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AM13" s="4"/>
     </row>
@@ -2923,7 +2929,7 @@
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AM14" s="4"/>
     </row>
@@ -2999,7 +3005,7 @@
       </c>
       <c r="AF15" s="4"/>
       <c r="AG15" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AM15" s="4"/>
     </row>
@@ -3075,7 +3081,7 @@
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AM16" s="4"/>
     </row>
@@ -3151,7 +3157,7 @@
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AM17" s="4"/>
     </row>
@@ -3227,7 +3233,7 @@
       </c>
       <c r="AF18" s="4"/>
       <c r="AG18" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AM18" s="4"/>
     </row>
@@ -3435,7 +3441,7 @@
       </c>
       <c r="AF21" s="4"/>
       <c r="AG21" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AM21" s="4"/>
     </row>
@@ -3507,7 +3513,7 @@
       </c>
       <c r="AF22" s="4"/>
       <c r="AG22" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AM22" s="4"/>
     </row>
@@ -3579,7 +3585,7 @@
       </c>
       <c r="AF23" s="4"/>
       <c r="AG23" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM23" s="4"/>
     </row>
@@ -3651,7 +3657,7 @@
       </c>
       <c r="AF24" s="4"/>
       <c r="AG24" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AM24" s="4"/>
     </row>
@@ -3723,7 +3729,7 @@
       </c>
       <c r="AF25" s="4"/>
       <c r="AG25" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AM25" s="4"/>
     </row>
@@ -3795,7 +3801,7 @@
       </c>
       <c r="AF26" s="4"/>
       <c r="AG26" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AM26" s="4"/>
     </row>
@@ -3867,7 +3873,7 @@
       </c>
       <c r="AF27" s="4"/>
       <c r="AG27" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AM27" s="4"/>
     </row>
@@ -4413,7 +4419,7 @@
         <v>157</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AM35" s="4"/>
     </row>
@@ -4422,7 +4428,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4495,16 +4501,16 @@
         <v>185</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH36" s="2" t="s">
         <v>187</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AM36" s="4"/>
     </row>
@@ -4513,7 +4519,7 @@
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4586,16 +4592,16 @@
         <v>185</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH37" s="2" t="s">
         <v>188</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AM37" s="4"/>
     </row>
@@ -4604,7 +4610,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4643,16 +4649,16 @@
         <v>138</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4678,16 +4684,16 @@
         <v>185</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>189</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.15">
@@ -4695,7 +4701,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -4734,16 +4740,16 @@
         <v>138</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -4769,16 +4775,16 @@
         <v>185</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AH39" s="2" t="s">
         <v>190</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.15">
@@ -4786,7 +4792,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -4825,16 +4831,16 @@
         <v>138</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -4860,16 +4866,16 @@
         <v>185</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AH40" s="2" t="s">
         <v>191</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.15">
@@ -4877,7 +4883,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -4916,16 +4922,16 @@
         <v>138</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -4951,16 +4957,16 @@
         <v>185</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AH41" s="2" t="s">
         <v>192</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="2:39" x14ac:dyDescent="0.15">
@@ -4968,7 +4974,7 @@
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -5007,16 +5013,16 @@
         <v>138</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5042,16 +5048,16 @@
         <v>185</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AH42" s="2" t="s">
         <v>193</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="2:39" x14ac:dyDescent="0.15">
@@ -5124,19 +5130,19 @@
         <v>158</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AH43" s="2" t="s">
         <v>194</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="2:39" x14ac:dyDescent="0.15">
@@ -5209,19 +5215,19 @@
         <v>158</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>195</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK44" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="2:39" x14ac:dyDescent="0.15">
@@ -5288,22 +5294,22 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AF45" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AH45" s="2" t="s">
         <v>196</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="2:39" x14ac:dyDescent="0.15">
@@ -5311,7 +5317,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5356,10 +5362,10 @@
         <v>138</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5379,22 +5385,22 @@
         <v>1</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AF46" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AH46" s="2" t="s">
         <v>197</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="2:39" x14ac:dyDescent="0.15">
@@ -5444,7 +5450,7 @@
         <v>138</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -5464,22 +5470,22 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF47" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AH47" s="2" t="s">
         <v>198</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="2:39" x14ac:dyDescent="0.15">
@@ -5552,16 +5558,16 @@
         <v>158</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="AH48" s="2" t="s">
         <v>199</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:37" x14ac:dyDescent="0.15">
@@ -5634,16 +5640,16 @@
         <v>158</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AH49" s="2" t="s">
         <v>200</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="2:37" x14ac:dyDescent="0.15">
@@ -5693,10 +5699,10 @@
         <v>138</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -5716,22 +5722,22 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF50" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AH50" s="2" t="s">
         <v>201</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="2:37" x14ac:dyDescent="0.15">
@@ -5807,16 +5813,16 @@
         <v>159</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AH51" s="2" t="s">
         <v>202</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="2:37" x14ac:dyDescent="0.15">
@@ -5892,16 +5898,16 @@
         <v>160</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>203</v>
+        <v>318</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="2:37" x14ac:dyDescent="0.15">
@@ -5972,16 +5978,16 @@
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="2:37" x14ac:dyDescent="0.15">
@@ -6057,19 +6063,19 @@
         <v>158</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK54" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="55" spans="2:37" x14ac:dyDescent="0.15">
@@ -6143,16 +6149,16 @@
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="2:37" x14ac:dyDescent="0.15">
@@ -6223,16 +6229,16 @@
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="2:37" x14ac:dyDescent="0.15">
@@ -6306,16 +6312,16 @@
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="2:37" x14ac:dyDescent="0.15">
@@ -6386,16 +6392,16 @@
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="2:37" x14ac:dyDescent="0.15">
@@ -6442,16 +6448,16 @@
         <v>138</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6475,16 +6481,16 @@
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AH59" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="2:37" x14ac:dyDescent="0.15">
@@ -6528,16 +6534,16 @@
         <v>138</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6561,16 +6567,16 @@
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AH60" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="2:37" x14ac:dyDescent="0.15">
@@ -6617,16 +6623,16 @@
         <v>138</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6650,16 +6656,16 @@
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AH61" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI61" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ61" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="2:37" x14ac:dyDescent="0.15">
@@ -6703,16 +6709,16 @@
         <v>138</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -6736,16 +6742,16 @@
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AH62" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI62" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ62" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="2:37" x14ac:dyDescent="0.15">
@@ -6792,16 +6798,16 @@
         <v>138</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -6826,16 +6832,16 @@
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AH63" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI63" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AI63" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="AJ63" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="2:37" x14ac:dyDescent="0.15">
@@ -6880,16 +6886,16 @@
         <v>138</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -6914,16 +6920,16 @@
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AH64" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI64" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="AI64" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="AJ64" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="2:39" x14ac:dyDescent="0.15">
@@ -6973,13 +6979,13 @@
         <v>134</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -7003,16 +7009,16 @@
       </c>
       <c r="AF65" s="4"/>
       <c r="AG65" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AH65" s="2" t="s">
         <v>192</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="2:39" x14ac:dyDescent="0.15">
@@ -7059,13 +7065,13 @@
         <v>126</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7089,16 +7095,16 @@
       </c>
       <c r="AF66" s="4"/>
       <c r="AG66" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AH66" s="2" t="s">
         <v>192</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ66" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="2:39" x14ac:dyDescent="0.15">
@@ -7148,13 +7154,13 @@
         <v>134</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7178,16 +7184,16 @@
       </c>
       <c r="AF67" s="4"/>
       <c r="AG67" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AH67" s="2" t="s">
         <v>193</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="2:39" x14ac:dyDescent="0.15">
@@ -7234,13 +7240,13 @@
         <v>126</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7264,16 +7270,16 @@
       </c>
       <c r="AF68" s="4"/>
       <c r="AG68" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AH68" s="2" t="s">
         <v>193</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AJ68" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="2:39" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0EFED7-06AD-4594-8427-6C7DB78EF258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431254C0-7106-445F-A992-5E8DA2A468C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="322">
   <si>
     <t>0</t>
   </si>
@@ -927,14 +927,6 @@
   </si>
   <si>
     <t>-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1213,6 +1205,9 @@
   <si>
     <t>4846-6/4846-6_28</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4298.prefab</t>
   </si>
 </sst>
 </file>
@@ -1791,19 +1786,19 @@
         <v>236</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>235</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>104</v>
@@ -1827,7 +1822,7 @@
         <v>161</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
@@ -1947,25 +1942,25 @@
         <v>237</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S3" s="8" t="s">
         <v>234</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>238</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>111</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>116</v>
@@ -2078,10 +2073,10 @@
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2153,10 +2148,10 @@
         <v>125</v>
       </c>
       <c r="M5" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>122</v>
@@ -2230,10 +2225,10 @@
         <v>126</v>
       </c>
       <c r="M6" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>124</v>
@@ -2306,10 +2301,10 @@
         <v>126</v>
       </c>
       <c r="M7" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>123</v>
@@ -2360,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2427,7 +2422,7 @@
       </c>
       <c r="AF8" s="4"/>
       <c r="AG8" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AH8" s="2" t="s">
         <v>130</v>
@@ -2439,7 +2434,7 @@
         <v>212</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AM8" s="4"/>
     </row>
@@ -2448,7 +2443,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2515,7 +2510,7 @@
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AH9" s="2" t="s">
         <v>130</v>
@@ -2527,7 +2522,7 @@
         <v>212</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AM9" s="4"/>
     </row>
@@ -2603,7 +2598,7 @@
       </c>
       <c r="AF10" s="4"/>
       <c r="AG10" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AH10" s="2" t="s">
         <v>130</v>
@@ -2615,7 +2610,7 @@
         <v>212</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AM10" s="4"/>
     </row>
@@ -2691,7 +2686,7 @@
       </c>
       <c r="AF11" s="4"/>
       <c r="AG11" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AH11" s="2" t="s">
         <v>186</v>
@@ -2776,7 +2771,7 @@
       </c>
       <c r="AF12" s="4"/>
       <c r="AG12" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AH12" s="2" t="s">
         <v>214</v>
@@ -2857,7 +2852,10 @@
       </c>
       <c r="AF13" s="4"/>
       <c r="AG13" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="AM13" s="4"/>
     </row>
@@ -2929,7 +2927,10 @@
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="AM14" s="4"/>
     </row>
@@ -3005,7 +3006,10 @@
       </c>
       <c r="AF15" s="4"/>
       <c r="AG15" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM15" s="4"/>
     </row>
@@ -3081,7 +3085,10 @@
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM16" s="4"/>
     </row>
@@ -3157,7 +3164,10 @@
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM17" s="4"/>
     </row>
@@ -3233,7 +3243,10 @@
       </c>
       <c r="AF18" s="4"/>
       <c r="AG18" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM18" s="4"/>
     </row>
@@ -3303,6 +3316,9 @@
       </c>
       <c r="AF19" s="4"/>
       <c r="AG19" s="4"/>
+      <c r="AJ19" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM19" s="4"/>
     </row>
     <row r="20" spans="2:39" x14ac:dyDescent="0.15">
@@ -3371,6 +3387,9 @@
       </c>
       <c r="AF20" s="4"/>
       <c r="AG20" s="4"/>
+      <c r="AJ20" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM20" s="4"/>
     </row>
     <row r="21" spans="2:39" x14ac:dyDescent="0.15">
@@ -3441,7 +3460,10 @@
       </c>
       <c r="AF21" s="4"/>
       <c r="AG21" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM21" s="4"/>
     </row>
@@ -3513,7 +3535,10 @@
       </c>
       <c r="AF22" s="4"/>
       <c r="AG22" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM22" s="4"/>
     </row>
@@ -3585,7 +3610,10 @@
       </c>
       <c r="AF23" s="4"/>
       <c r="AG23" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM23" s="4"/>
     </row>
@@ -3657,7 +3685,10 @@
       </c>
       <c r="AF24" s="4"/>
       <c r="AG24" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM24" s="4"/>
     </row>
@@ -3729,7 +3760,10 @@
       </c>
       <c r="AF25" s="4"/>
       <c r="AG25" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM25" s="4"/>
     </row>
@@ -3801,7 +3835,10 @@
       </c>
       <c r="AF26" s="4"/>
       <c r="AG26" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM26" s="4"/>
     </row>
@@ -3873,7 +3910,10 @@
       </c>
       <c r="AF27" s="4"/>
       <c r="AG27" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM27" s="4"/>
     </row>
@@ -3943,6 +3983,9 @@
       </c>
       <c r="AF28" s="4"/>
       <c r="AG28" s="4"/>
+      <c r="AJ28" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM28" s="4"/>
     </row>
     <row r="29" spans="2:39" x14ac:dyDescent="0.15">
@@ -4011,6 +4054,9 @@
       </c>
       <c r="AF29" s="4"/>
       <c r="AG29" s="4"/>
+      <c r="AJ29" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM29" s="4"/>
     </row>
     <row r="30" spans="2:39" x14ac:dyDescent="0.15">
@@ -4077,6 +4123,9 @@
       </c>
       <c r="AF30" s="4"/>
       <c r="AG30" s="4"/>
+      <c r="AJ30" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM30" s="4"/>
     </row>
     <row r="31" spans="2:39" x14ac:dyDescent="0.15">
@@ -4145,6 +4194,9 @@
       </c>
       <c r="AF31" s="4"/>
       <c r="AG31" s="4"/>
+      <c r="AJ31" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM31" s="4"/>
     </row>
     <row r="32" spans="2:39" x14ac:dyDescent="0.15">
@@ -4211,6 +4263,9 @@
       </c>
       <c r="AF32" s="4"/>
       <c r="AG32" s="4"/>
+      <c r="AJ32" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM32" s="4"/>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.15">
@@ -4279,6 +4334,9 @@
       </c>
       <c r="AF33" s="4"/>
       <c r="AG33" s="4"/>
+      <c r="AJ33" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM33" s="4"/>
     </row>
     <row r="34" spans="2:39" x14ac:dyDescent="0.15">
@@ -4347,6 +4405,9 @@
       </c>
       <c r="AF34" s="4"/>
       <c r="AG34" s="4"/>
+      <c r="AJ34" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AM34" s="4"/>
     </row>
     <row r="35" spans="2:39" x14ac:dyDescent="0.15">
@@ -4419,7 +4480,10 @@
         <v>157</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AM35" s="4"/>
     </row>
@@ -4501,7 +4565,7 @@
         <v>185</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AH36" s="2" t="s">
         <v>187</v>
@@ -4592,7 +4656,7 @@
         <v>185</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AH37" s="2" t="s">
         <v>188</v>
@@ -4649,16 +4713,13 @@
         <v>138</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4684,7 +4745,7 @@
         <v>185</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>189</v>
@@ -4740,16 +4801,16 @@
         <v>138</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -4775,7 +4836,7 @@
         <v>185</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AH39" s="2" t="s">
         <v>190</v>
@@ -4831,16 +4892,16 @@
         <v>138</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>241</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -4866,7 +4927,7 @@
         <v>185</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH40" s="2" t="s">
         <v>191</v>
@@ -4922,16 +4983,16 @@
         <v>138</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>242</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -4957,7 +5018,7 @@
         <v>185</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH41" s="2" t="s">
         <v>192</v>
@@ -5013,16 +5074,16 @@
         <v>138</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>243</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5048,7 +5109,7 @@
         <v>185</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AH42" s="2" t="s">
         <v>193</v>
@@ -5130,7 +5191,7 @@
         <v>158</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AH43" s="2" t="s">
         <v>194</v>
@@ -5215,7 +5276,7 @@
         <v>158</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>195</v>
@@ -5294,13 +5355,13 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AF45" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AH45" s="2" t="s">
         <v>196</v>
@@ -5317,7 +5378,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5361,11 +5422,8 @@
       <c r="T46" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="U46" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="V46" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5385,13 +5443,13 @@
         <v>1</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AF46" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AH46" s="2" t="s">
         <v>197</v>
@@ -5470,13 +5528,13 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AF47" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AH47" s="2" t="s">
         <v>198</v>
@@ -5558,7 +5616,7 @@
         <v>158</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AH48" s="2" t="s">
         <v>199</v>
@@ -5640,7 +5698,7 @@
         <v>158</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AH49" s="2" t="s">
         <v>200</v>
@@ -5699,10 +5757,7 @@
         <v>138</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="U50" s="2" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -5722,13 +5777,13 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AF50" s="4" t="s">
         <v>158</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AH50" s="2" t="s">
         <v>201</v>
@@ -5813,7 +5868,7 @@
         <v>159</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AH51" s="2" t="s">
         <v>202</v>
@@ -5898,10 +5953,10 @@
         <v>160</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AI52" s="2" t="s">
         <v>210</v>
@@ -5978,7 +6033,7 @@
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AH53" s="2" t="s">
         <v>203</v>
@@ -6063,7 +6118,7 @@
         <v>158</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AH54" s="2" t="s">
         <v>204</v>
@@ -6149,7 +6204,7 @@
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AH55" s="2" t="s">
         <v>205</v>
@@ -6229,7 +6284,7 @@
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AH56" s="2" t="s">
         <v>205</v>
@@ -6312,7 +6367,7 @@
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AH57" s="2" t="s">
         <v>206</v>
@@ -6392,7 +6447,7 @@
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AH58" s="2" t="s">
         <v>206</v>
@@ -6448,16 +6503,16 @@
         <v>138</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="U59" s="2" t="s">
         <v>244</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6481,7 +6536,7 @@
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AH59" s="2" t="s">
         <v>207</v>
@@ -6534,16 +6589,16 @@
         <v>138</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="U60" s="2" t="s">
         <v>244</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6567,7 +6622,7 @@
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AH60" s="2" t="s">
         <v>207</v>
@@ -6623,16 +6678,16 @@
         <v>138</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="U61" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6656,7 +6711,7 @@
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AH61" s="2" t="s">
         <v>208</v>
@@ -6709,16 +6764,16 @@
         <v>138</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="U62" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -6742,7 +6797,7 @@
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AH62" s="2" t="s">
         <v>208</v>
@@ -6798,16 +6853,16 @@
         <v>138</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U63" s="2" t="s">
         <v>241</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -6832,7 +6887,7 @@
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH63" s="2" t="s">
         <v>209</v>
@@ -6886,16 +6941,16 @@
         <v>138</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>241</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -6920,7 +6975,7 @@
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH64" s="2" t="s">
         <v>209</v>
@@ -6979,13 +7034,13 @@
         <v>134</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>242</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -7009,7 +7064,7 @@
       </c>
       <c r="AF65" s="4"/>
       <c r="AG65" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH65" s="2" t="s">
         <v>192</v>
@@ -7065,13 +7120,13 @@
         <v>126</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="U66" s="2" t="s">
         <v>242</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7095,7 +7150,7 @@
       </c>
       <c r="AF66" s="4"/>
       <c r="AG66" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH66" s="2" t="s">
         <v>192</v>
@@ -7154,13 +7209,13 @@
         <v>134</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U67" s="2" t="s">
         <v>243</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7184,7 +7239,7 @@
       </c>
       <c r="AF67" s="4"/>
       <c r="AG67" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AH67" s="2" t="s">
         <v>193</v>
@@ -7240,13 +7295,13 @@
         <v>126</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>243</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7270,7 +7325,7 @@
       </c>
       <c r="AF68" s="4"/>
       <c r="AG68" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AH68" s="2" t="s">
         <v>193</v>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431254C0-7106-445F-A992-5E8DA2A468C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830D72B4-C229-4472-9C32-5A48ADFF8B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="323">
   <si>
     <t>0</t>
   </si>
@@ -1208,6 +1208,9 @@
   </si>
   <si>
     <t>Assets/Model/Prefab/4298.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4308.prefab</t>
   </si>
 </sst>
 </file>
@@ -2854,6 +2857,12 @@
       <c r="AG13" s="2" t="s">
         <v>282</v>
       </c>
+      <c r="AH13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ13" s="2" t="s">
         <v>212</v>
       </c>
@@ -2929,6 +2938,12 @@
       <c r="AG14" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="AH14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ14" s="2" t="s">
         <v>212</v>
       </c>
@@ -2964,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>138</v>
@@ -3008,6 +3023,12 @@
       <c r="AG15" s="2" t="s">
         <v>284</v>
       </c>
+      <c r="AH15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ15" s="2" t="s">
         <v>321</v>
       </c>
@@ -3087,6 +3108,12 @@
       <c r="AG16" s="2" t="s">
         <v>285</v>
       </c>
+      <c r="AH16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ16" s="2" t="s">
         <v>321</v>
       </c>
@@ -3166,6 +3193,12 @@
       <c r="AG17" s="2" t="s">
         <v>286</v>
       </c>
+      <c r="AH17" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ17" s="2" t="s">
         <v>321</v>
       </c>
@@ -3245,6 +3278,12 @@
       <c r="AG18" s="2" t="s">
         <v>287</v>
       </c>
+      <c r="AH18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ18" s="2" t="s">
         <v>321</v>
       </c>
@@ -3316,6 +3355,12 @@
       </c>
       <c r="AF19" s="4"/>
       <c r="AG19" s="4"/>
+      <c r="AH19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ19" s="2" t="s">
         <v>321</v>
       </c>
@@ -3387,6 +3432,12 @@
       </c>
       <c r="AF20" s="4"/>
       <c r="AG20" s="4"/>
+      <c r="AH20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="AJ20" s="2" t="s">
         <v>321</v>
       </c>
@@ -3462,6 +3513,12 @@
       <c r="AG21" s="2" t="s">
         <v>288</v>
       </c>
+      <c r="AH21" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ21" s="2" t="s">
         <v>321</v>
       </c>
@@ -3537,6 +3594,12 @@
       <c r="AG22" s="2" t="s">
         <v>289</v>
       </c>
+      <c r="AH22" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ22" s="2" t="s">
         <v>321</v>
       </c>
@@ -3612,6 +3675,12 @@
       <c r="AG23" s="2" t="s">
         <v>290</v>
       </c>
+      <c r="AH23" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ23" s="2" t="s">
         <v>321</v>
       </c>
@@ -3687,6 +3756,12 @@
       <c r="AG24" s="2" t="s">
         <v>291</v>
       </c>
+      <c r="AH24" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ24" s="2" t="s">
         <v>321</v>
       </c>
@@ -3762,6 +3837,12 @@
       <c r="AG25" s="2" t="s">
         <v>292</v>
       </c>
+      <c r="AH25" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI25" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ25" s="2" t="s">
         <v>321</v>
       </c>
@@ -3837,6 +3918,12 @@
       <c r="AG26" s="2" t="s">
         <v>293</v>
       </c>
+      <c r="AH26" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI26" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ26" s="2" t="s">
         <v>321</v>
       </c>
@@ -3912,6 +3999,12 @@
       <c r="AG27" s="2" t="s">
         <v>294</v>
       </c>
+      <c r="AH27" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI27" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ27" s="2" t="s">
         <v>321</v>
       </c>
@@ -3983,6 +4076,12 @@
       </c>
       <c r="AF28" s="4"/>
       <c r="AG28" s="4"/>
+      <c r="AH28" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI28" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ28" s="2" t="s">
         <v>321</v>
       </c>
@@ -4054,6 +4153,12 @@
       </c>
       <c r="AF29" s="4"/>
       <c r="AG29" s="4"/>
+      <c r="AH29" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI29" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ29" s="2" t="s">
         <v>321</v>
       </c>
@@ -4123,6 +4228,12 @@
       </c>
       <c r="AF30" s="4"/>
       <c r="AG30" s="4"/>
+      <c r="AH30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI30" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ30" s="2" t="s">
         <v>321</v>
       </c>
@@ -4194,6 +4305,12 @@
       </c>
       <c r="AF31" s="4"/>
       <c r="AG31" s="4"/>
+      <c r="AH31" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI31" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ31" s="2" t="s">
         <v>321</v>
       </c>
@@ -4263,6 +4380,12 @@
       </c>
       <c r="AF32" s="4"/>
       <c r="AG32" s="4"/>
+      <c r="AH32" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI32" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ32" s="2" t="s">
         <v>321</v>
       </c>
@@ -4334,6 +4457,12 @@
       </c>
       <c r="AF33" s="4"/>
       <c r="AG33" s="4"/>
+      <c r="AH33" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI33" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ33" s="2" t="s">
         <v>321</v>
       </c>
@@ -4405,6 +4534,12 @@
       </c>
       <c r="AF34" s="4"/>
       <c r="AG34" s="4"/>
+      <c r="AH34" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI34" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="AJ34" s="2" t="s">
         <v>321</v>
       </c>
@@ -4481,6 +4616,12 @@
       </c>
       <c r="AG35" s="2" t="s">
         <v>295</v>
+      </c>
+      <c r="AH35" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AI35" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AJ35" s="2" t="s">
         <v>321</v>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830D72B4-C229-4472-9C32-5A48ADFF8B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCC11B7-82B1-4486-AC51-FFB38DFCED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4590" yWindow="1110" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="325">
   <si>
     <t>0</t>
   </si>
@@ -950,22 +950,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可自动探索人材、登庸武将</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可巡视领地增加治安，并可以少额的资金设置军事设施、障碍物、陷阱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可使部份俘虏的忠诚变得容易下降,并且尝试招募俘虏</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>巡查局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>productCost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1211,6 +1199,26 @@
   </si>
   <si>
     <t>Assets/Model/Prefab/4308.prefab</t>
+  </si>
+  <si>
+    <t>军事府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可自动探索人材、登庸本城武将和俘虏。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可巡视领地增加治安，训练士兵气力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limitType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4485.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1712,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AN120"/>
+  <dimension ref="A1:AO120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
@@ -1732,17 +1740,17 @@
     <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
     <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="71.875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.875" style="2" customWidth="1"/>
-    <col min="36" max="36" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="164.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9" style="2"/>
+    <col min="30" max="30" width="16.125" style="2" customWidth="1"/>
+    <col min="31" max="33" width="71.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="37.875" style="2" customWidth="1"/>
+    <col min="37" max="37" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="164.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1789,19 +1797,19 @@
         <v>236</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>235</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="U1" s="7" t="s">
         <v>245</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>104</v>
@@ -1830,14 +1838,12 @@
       <c r="AE1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AF1" s="14" t="s">
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="AH1" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="AI1" s="9" t="s">
         <v>52</v>
@@ -1845,12 +1851,15 @@
       <c r="AJ1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="AK1" s="9"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="9"/>
-      <c r="AN1" s="7"/>
-    </row>
-    <row r="2" spans="1:40" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AK1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="7"/>
+    </row>
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1885,7 +1894,7 @@
       <c r="AD2"/>
       <c r="AE2"/>
       <c r="AF2"/>
-      <c r="AG2" s="2"/>
+      <c r="AG2"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -1893,8 +1902,9 @@
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
-    </row>
-    <row r="3" spans="1:40" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AO2" s="2"/>
+    </row>
+    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1945,25 +1955,25 @@
         <v>237</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="S3" s="8" t="s">
         <v>234</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>238</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>111</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>116</v>
@@ -1987,28 +1997,31 @@
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="AG3" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="AG3" s="13" t="s">
+      <c r="AH3" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="AH3" s="13" t="s">
+      <c r="AI3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AI3" s="13" t="s">
+      <c r="AJ3" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="AJ3" s="13" t="s">
+      <c r="AK3" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AK3" s="8" t="s">
+      <c r="AL3" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="AL3" s="8"/>
       <c r="AM3" s="8"/>
       <c r="AN3" s="8"/>
-    </row>
-    <row r="4" spans="1:40" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AO3" s="8"/>
+    </row>
+    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2076,10 +2089,10 @@
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2103,9 +2116,9 @@
         <v>5</v>
       </c>
       <c r="AF4" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="AH4" s="11" t="s">
@@ -2118,10 +2131,13 @@
         <v>5</v>
       </c>
       <c r="AK4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2151,10 +2167,10 @@
         <v>125</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>122</v>
@@ -2195,9 +2211,10 @@
       </c>
       <c r="AF5" s="4"/>
       <c r="AG5" s="4"/>
-      <c r="AM5" s="4"/>
-    </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AH5" s="4"/>
+      <c r="AN5" s="4"/>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2228,10 +2245,10 @@
         <v>126</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>124</v>
@@ -2272,9 +2289,10 @@
       </c>
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
-      <c r="AM6" s="4"/>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AH6" s="4"/>
+      <c r="AN6" s="4"/>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -2304,10 +2322,10 @@
         <v>126</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>123</v>
@@ -2348,9 +2366,10 @@
       </c>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
-      <c r="AM7" s="4"/>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AH7" s="4"/>
+      <c r="AN7" s="4"/>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>121</v>
       </c>
@@ -2358,7 +2377,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2424,29 +2443,30 @@
         <v>60</v>
       </c>
       <c r="AF8" s="4"/>
-      <c r="AG8" s="2" t="s">
-        <v>277</v>
-      </c>
+      <c r="AG8" s="4"/>
       <c r="AH8" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="AJ8" s="2" t="s">
         <v>212</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="AM8" s="4"/>
-    </row>
-    <row r="9" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AN8" s="4"/>
+    </row>
+    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2512,24 +2532,25 @@
         <v>154</v>
       </c>
       <c r="AF9" s="4"/>
-      <c r="AG9" s="2" t="s">
-        <v>278</v>
-      </c>
+      <c r="AG9" s="4"/>
       <c r="AH9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="AJ9" s="2" t="s">
         <v>212</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="AM9" s="4"/>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="AN9" s="4"/>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2600,24 +2621,25 @@
         <v>61</v>
       </c>
       <c r="AF10" s="4"/>
-      <c r="AG10" s="2" t="s">
-        <v>279</v>
-      </c>
+      <c r="AG10" s="4"/>
       <c r="AH10" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI10" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="AI10" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="AJ10" s="2" t="s">
         <v>212</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AM10" s="4"/>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AN10" s="4"/>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2688,21 +2710,22 @@
         <v>62</v>
       </c>
       <c r="AF11" s="4"/>
-      <c r="AG11" s="2" t="s">
-        <v>280</v>
-      </c>
+      <c r="AG11" s="4"/>
       <c r="AH11" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI11" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="AI11" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="AJ11" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="AM11" s="4"/>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AK11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AN11" s="4"/>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2773,21 +2796,22 @@
         <v>63</v>
       </c>
       <c r="AF12" s="4"/>
-      <c r="AG12" s="2" t="s">
-        <v>281</v>
-      </c>
+      <c r="AG12" s="4"/>
       <c r="AH12" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI12" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="AI12" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="AJ12" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="AM12" s="4"/>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AK12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AN12" s="4"/>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2854,21 +2878,22 @@
         <v>64</v>
       </c>
       <c r="AF13" s="4"/>
-      <c r="AG13" s="2" t="s">
-        <v>282</v>
-      </c>
+      <c r="AG13" s="4"/>
       <c r="AH13" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI13" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="AI13" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="AJ13" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AM13" s="4"/>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AK13" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AN13" s="4"/>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2935,21 +2960,22 @@
         <v>65</v>
       </c>
       <c r="AF14" s="4"/>
-      <c r="AG14" s="2" t="s">
-        <v>283</v>
-      </c>
+      <c r="AG14" s="4"/>
       <c r="AH14" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI14" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="AI14" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="AJ14" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AM14" s="4"/>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="AK14" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AN14" s="4"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -3020,21 +3046,22 @@
         <v>66</v>
       </c>
       <c r="AF15" s="4"/>
-      <c r="AG15" s="2" t="s">
-        <v>284</v>
-      </c>
+      <c r="AG15" s="4"/>
       <c r="AH15" s="2" t="s">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM15" s="4"/>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN15" s="4"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3105,21 +3132,22 @@
         <v>67</v>
       </c>
       <c r="AF16" s="4"/>
-      <c r="AG16" s="2" t="s">
-        <v>285</v>
-      </c>
+      <c r="AG16" s="4"/>
       <c r="AH16" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AI16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AI16" s="2" t="s">
+      <c r="AJ16" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ16" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM16" s="4"/>
-    </row>
-    <row r="17" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK16" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN16" s="4"/>
+    </row>
+    <row r="17" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3190,21 +3218,22 @@
         <v>68</v>
       </c>
       <c r="AF17" s="4"/>
-      <c r="AG17" s="2" t="s">
-        <v>286</v>
-      </c>
+      <c r="AG17" s="4"/>
       <c r="AH17" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AI17" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AI17" s="2" t="s">
+      <c r="AJ17" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ17" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM17" s="4"/>
-    </row>
-    <row r="18" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AK17" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN17" s="4"/>
+    </row>
+    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3275,21 +3304,22 @@
         <v>69</v>
       </c>
       <c r="AF18" s="4"/>
-      <c r="AG18" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="AG18" s="4"/>
       <c r="AH18" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AI18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AI18" s="2" t="s">
+      <c r="AJ18" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ18" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM18" s="4"/>
-    </row>
-    <row r="19" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK18" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN18" s="4"/>
+    </row>
+    <row r="19" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -3355,18 +3385,19 @@
       </c>
       <c r="AF19" s="4"/>
       <c r="AG19" s="4"/>
-      <c r="AH19" s="2" t="s">
+      <c r="AH19" s="4"/>
+      <c r="AI19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AI19" s="2" t="s">
+      <c r="AJ19" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ19" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM19" s="4"/>
-    </row>
-    <row r="20" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK19" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN19" s="4"/>
+    </row>
+    <row r="20" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3432,18 +3463,19 @@
       </c>
       <c r="AF20" s="4"/>
       <c r="AG20" s="4"/>
-      <c r="AH20" s="2" t="s">
+      <c r="AH20" s="4"/>
+      <c r="AI20" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AI20" s="2" t="s">
+      <c r="AJ20" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AJ20" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM20" s="4"/>
-    </row>
-    <row r="21" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK20" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN20" s="4"/>
+    </row>
+    <row r="21" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -3510,21 +3542,22 @@
         <v>72</v>
       </c>
       <c r="AF21" s="4"/>
-      <c r="AG21" s="2" t="s">
-        <v>288</v>
-      </c>
+      <c r="AG21" s="4"/>
       <c r="AH21" s="2" t="s">
-        <v>322</v>
+        <v>285</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM21" s="4"/>
-    </row>
-    <row r="22" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN21" s="4"/>
+    </row>
+    <row r="22" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -3591,21 +3624,22 @@
         <v>73</v>
       </c>
       <c r="AF22" s="4"/>
-      <c r="AG22" s="2" t="s">
-        <v>289</v>
-      </c>
+      <c r="AG22" s="4"/>
       <c r="AH22" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM22" s="4"/>
-    </row>
-    <row r="23" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK22" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN22" s="4"/>
+    </row>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3672,21 +3706,22 @@
         <v>74</v>
       </c>
       <c r="AF23" s="4"/>
-      <c r="AG23" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="AG23" s="4"/>
       <c r="AH23" s="2" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM23" s="4"/>
-    </row>
-    <row r="24" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK23" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN23" s="4"/>
+    </row>
+    <row r="24" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3753,21 +3788,22 @@
         <v>75</v>
       </c>
       <c r="AF24" s="4"/>
-      <c r="AG24" s="2" t="s">
-        <v>291</v>
-      </c>
+      <c r="AG24" s="4"/>
       <c r="AH24" s="2" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM24" s="4"/>
-    </row>
-    <row r="25" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN24" s="4"/>
+    </row>
+    <row r="25" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3834,21 +3870,22 @@
         <v>76</v>
       </c>
       <c r="AF25" s="4"/>
-      <c r="AG25" s="2" t="s">
-        <v>292</v>
-      </c>
+      <c r="AG25" s="4"/>
       <c r="AH25" s="2" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM25" s="4"/>
-    </row>
-    <row r="26" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK25" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN25" s="4"/>
+    </row>
+    <row r="26" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3915,21 +3952,22 @@
         <v>77</v>
       </c>
       <c r="AF26" s="4"/>
-      <c r="AG26" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="AG26" s="4"/>
       <c r="AH26" s="2" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM26" s="4"/>
-    </row>
-    <row r="27" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK26" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN26" s="4"/>
+    </row>
+    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -3996,21 +4034,22 @@
         <v>78</v>
       </c>
       <c r="AF27" s="4"/>
-      <c r="AG27" s="2" t="s">
-        <v>294</v>
-      </c>
+      <c r="AG27" s="4"/>
       <c r="AH27" s="2" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM27" s="4"/>
-    </row>
-    <row r="28" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK27" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN27" s="4"/>
+    </row>
+    <row r="28" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -4076,18 +4115,19 @@
       </c>
       <c r="AF28" s="4"/>
       <c r="AG28" s="4"/>
-      <c r="AH28" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH28" s="4"/>
       <c r="AI28" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM28" s="4"/>
-    </row>
-    <row r="29" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK28" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN28" s="4"/>
+    </row>
+    <row r="29" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -4153,18 +4193,19 @@
       </c>
       <c r="AF29" s="4"/>
       <c r="AG29" s="4"/>
-      <c r="AH29" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH29" s="4"/>
       <c r="AI29" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM29" s="4"/>
-    </row>
-    <row r="30" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK29" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN29" s="4"/>
+    </row>
+    <row r="30" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4228,18 +4269,19 @@
       </c>
       <c r="AF30" s="4"/>
       <c r="AG30" s="4"/>
-      <c r="AH30" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH30" s="4"/>
       <c r="AI30" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM30" s="4"/>
-    </row>
-    <row r="31" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK30" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN30" s="4"/>
+    </row>
+    <row r="31" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4305,18 +4347,19 @@
       </c>
       <c r="AF31" s="4"/>
       <c r="AG31" s="4"/>
-      <c r="AH31" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH31" s="4"/>
       <c r="AI31" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM31" s="4"/>
-    </row>
-    <row r="32" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK31" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN31" s="4"/>
+    </row>
+    <row r="32" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4380,18 +4423,19 @@
       </c>
       <c r="AF32" s="4"/>
       <c r="AG32" s="4"/>
-      <c r="AH32" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH32" s="4"/>
       <c r="AI32" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM32" s="4"/>
-    </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK32" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN32" s="4"/>
+    </row>
+    <row r="33" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4457,18 +4501,19 @@
       </c>
       <c r="AF33" s="4"/>
       <c r="AG33" s="4"/>
-      <c r="AH33" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH33" s="4"/>
       <c r="AI33" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM33" s="4"/>
-    </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK33" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN33" s="4"/>
+    </row>
+    <row r="34" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4534,18 +4579,19 @@
       </c>
       <c r="AF34" s="4"/>
       <c r="AG34" s="4"/>
-      <c r="AH34" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="AH34" s="4"/>
       <c r="AI34" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM34" s="4"/>
-    </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK34" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN34" s="4"/>
+    </row>
+    <row r="35" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4611,24 +4657,25 @@
       <c r="AE35" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AF35" s="4" t="s">
+      <c r="AF35" s="4"/>
+      <c r="AG35" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AG35" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="AH35" s="2" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AM35" s="4"/>
-    </row>
-    <row r="36" spans="2:39" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+      <c r="AK35" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AN35" s="4"/>
+    </row>
+    <row r="36" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B36" s="4">
         <v>32</v>
       </c>
@@ -4702,24 +4749,25 @@
       <c r="AE36" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AF36" s="4" t="s">
+      <c r="AF36" s="4"/>
+      <c r="AG36" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG36" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="AH36" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AI36" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="AI36" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="AJ36" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AM36" s="4"/>
-    </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK36" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN36" s="4"/>
+    </row>
+    <row r="37" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -4793,24 +4841,25 @@
       <c r="AE37" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AF37" s="4" t="s">
+      <c r="AF37" s="4"/>
+      <c r="AG37" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG37" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="AH37" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI37" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="AI37" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="AJ37" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="AM37" s="4"/>
-    </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK37" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN37" s="4"/>
+    </row>
+    <row r="38" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B38" s="4">
         <v>34</v>
       </c>
@@ -4854,13 +4903,13 @@
         <v>138</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4882,23 +4931,24 @@
       <c r="AE38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AF38" s="4" t="s">
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="AH38" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI38" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="AI38" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK38" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -4942,16 +4992,16 @@
         <v>138</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -4973,23 +5023,24 @@
       <c r="AE39" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AF39" s="4" t="s">
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG39" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="AH39" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AI39" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="AI39" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ39" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK39" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B40" s="4">
         <v>36</v>
       </c>
@@ -5033,16 +5084,16 @@
         <v>138</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>241</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -5064,23 +5115,24 @@
       <c r="AE40" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AF40" s="4" t="s">
+      <c r="AF40" s="4"/>
+      <c r="AG40" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG40" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="AH40" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="AI40" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="AI40" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ40" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK40" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B41" s="4">
         <v>37</v>
       </c>
@@ -5124,16 +5176,16 @@
         <v>138</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>242</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -5155,23 +5207,24 @@
       <c r="AE41" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AF41" s="4" t="s">
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG41" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="AH41" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AI41" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="AI41" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ41" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK41" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B42" s="4">
         <v>38</v>
       </c>
@@ -5215,16 +5268,16 @@
         <v>138</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>243</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5246,23 +5299,24 @@
       <c r="AE42" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AF42" s="4" t="s">
+      <c r="AF42" s="4"/>
+      <c r="AG42" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AG42" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="AH42" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI42" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="AI42" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ42" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK42" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5328,26 +5382,29 @@
       <c r="AE43" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AF43" s="4" t="s">
+      <c r="AF43" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG43" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="AH43" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="AI43" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="AI43" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ43" s="2" t="s">
         <v>210</v>
       </c>
       <c r="AK43" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL43" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B44" s="4">
         <v>40</v>
       </c>
@@ -5413,26 +5470,29 @@
       <c r="AE44" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AF44" s="4" t="s">
+      <c r="AF44" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG44" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="AH44" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="AI44" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="AI44" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ44" s="2" t="s">
         <v>210</v>
       </c>
       <c r="AK44" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL44" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5449,7 +5509,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J45" s="4">
         <v>0</v>
@@ -5496,30 +5556,33 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="AF45" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="AF45" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG45" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="AH45" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="AI45" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="AI45" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ45" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK45" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B46" s="4">
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5531,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J46" s="4">
         <v>0</v>
@@ -5564,7 +5627,7 @@
         <v>138</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5581,28 +5644,31 @@
         <v>30</v>
       </c>
       <c r="AD46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="AF46" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="AF46" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG46" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG46" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="AH46" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI46" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="AI46" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ46" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK46" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5619,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J47" s="4">
         <v>0</v>
@@ -5669,25 +5735,28 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="AF47" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="AF47" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG47" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="AH47" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="AI47" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="AI47" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ47" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK47" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5704,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J48" s="4">
         <v>0</v>
@@ -5753,23 +5822,26 @@
       <c r="AE48" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF48" s="4" t="s">
+      <c r="AF48" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG48" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="AH48" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI48" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="AI48" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ48" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="49" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK48" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -5786,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J49" s="4">
         <v>0</v>
@@ -5835,23 +5907,26 @@
       <c r="AE49" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AF49" s="4" t="s">
+      <c r="AF49" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG49" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG49" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="AH49" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI49" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="AI49" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ49" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="50" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK49" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B50" s="4">
         <v>46</v>
       </c>
@@ -5868,7 +5943,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J50" s="4">
         <v>0</v>
@@ -5898,7 +5973,7 @@
         <v>138</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -5920,23 +5995,26 @@
       <c r="AE50" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="AF50" s="4" t="s">
+      <c r="AF50" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG50" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="AH50" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="AI50" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="AI50" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ50" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="51" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK50" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -6005,23 +6083,26 @@
       <c r="AE51" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="AF51" s="4" t="s">
+      <c r="AF51" s="4">
+        <v>3</v>
+      </c>
+      <c r="AG51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="AG51" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="AH51" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="AI51" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="AI51" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ51" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="52" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK51" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -6090,23 +6171,26 @@
       <c r="AE52" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="AF52" s="4" t="s">
+      <c r="AF52" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG52" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="AG52" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="AH52" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>210</v>
+        <v>313</v>
       </c>
       <c r="AJ52" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="53" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK52" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -6173,20 +6257,21 @@
         <v>99</v>
       </c>
       <c r="AF53" s="4"/>
-      <c r="AG53" s="2" t="s">
-        <v>317</v>
-      </c>
+      <c r="AG53" s="4"/>
       <c r="AH53" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AI53" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="AI53" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ53" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="54" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK53" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -6255,26 +6340,29 @@
       <c r="AE54" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AF54" s="4" t="s">
+      <c r="AF54" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG54" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="AH54" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="AI54" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="AI54" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ54" s="2" t="s">
         <v>210</v>
       </c>
       <c r="AK54" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL54" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="2:37" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6344,20 +6432,21 @@
         <v>101</v>
       </c>
       <c r="AF55" s="4"/>
-      <c r="AG55" s="2" t="s">
-        <v>296</v>
-      </c>
+      <c r="AG55" s="4"/>
       <c r="AH55" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AI55" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="AI55" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ55" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="56" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK55" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6424,20 +6513,21 @@
         <v>101</v>
       </c>
       <c r="AF56" s="4"/>
-      <c r="AG56" s="2" t="s">
-        <v>296</v>
-      </c>
+      <c r="AG56" s="4"/>
       <c r="AH56" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AI56" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="AI56" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ56" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="57" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK56" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6507,20 +6597,21 @@
         <v>101</v>
       </c>
       <c r="AF57" s="4"/>
-      <c r="AG57" s="2" t="s">
-        <v>297</v>
-      </c>
+      <c r="AG57" s="4"/>
       <c r="AH57" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI57" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="AI57" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ57" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="58" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK57" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6587,20 +6678,21 @@
         <v>101</v>
       </c>
       <c r="AF58" s="4"/>
-      <c r="AG58" s="2" t="s">
-        <v>297</v>
-      </c>
+      <c r="AG58" s="4"/>
       <c r="AH58" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI58" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="AI58" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ58" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="59" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK58" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6644,16 +6736,16 @@
         <v>138</v>
       </c>
       <c r="S59" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="T59" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="T59" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="U59" s="2" t="s">
         <v>244</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6676,20 +6768,21 @@
         <v>101</v>
       </c>
       <c r="AF59" s="4"/>
-      <c r="AG59" s="2" t="s">
-        <v>298</v>
-      </c>
+      <c r="AG59" s="4"/>
       <c r="AH59" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI59" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="AI59" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ59" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="60" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK59" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6730,16 +6823,16 @@
         <v>138</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="U60" s="2" t="s">
         <v>244</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6762,20 +6855,21 @@
         <v>101</v>
       </c>
       <c r="AF60" s="4"/>
-      <c r="AG60" s="2" t="s">
-        <v>298</v>
-      </c>
+      <c r="AG60" s="4"/>
       <c r="AH60" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI60" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="AI60" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ60" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="61" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK60" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -6819,16 +6913,16 @@
         <v>138</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="U61" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6851,20 +6945,21 @@
         <v>101</v>
       </c>
       <c r="AF61" s="4"/>
-      <c r="AG61" s="2" t="s">
-        <v>299</v>
-      </c>
+      <c r="AG61" s="4"/>
       <c r="AH61" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AI61" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="AI61" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ61" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="62" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK61" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -6905,16 +7000,16 @@
         <v>138</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="U62" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -6937,20 +7032,21 @@
         <v>101</v>
       </c>
       <c r="AF62" s="4"/>
-      <c r="AG62" s="2" t="s">
-        <v>299</v>
-      </c>
+      <c r="AG62" s="4"/>
       <c r="AH62" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AI62" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="AI62" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ62" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="63" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK62" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -6994,16 +7090,16 @@
         <v>138</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="U63" s="2" t="s">
         <v>241</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -7027,20 +7123,21 @@
         <v>101</v>
       </c>
       <c r="AF63" s="4"/>
-      <c r="AG63" s="2" t="s">
-        <v>300</v>
-      </c>
+      <c r="AG63" s="4"/>
       <c r="AH63" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="AI63" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="AI63" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ63" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="64" spans="2:37" x14ac:dyDescent="0.15">
+      <c r="AK63" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -7082,16 +7179,16 @@
         <v>138</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>241</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -7115,20 +7212,21 @@
         <v>101</v>
       </c>
       <c r="AF64" s="4"/>
-      <c r="AG64" s="2" t="s">
-        <v>300</v>
-      </c>
+      <c r="AG64" s="4"/>
       <c r="AH64" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="AI64" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="AI64" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ64" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK64" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B65" s="4">
         <v>61</v>
       </c>
@@ -7175,13 +7273,13 @@
         <v>134</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>242</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -7204,20 +7302,21 @@
         <v>91</v>
       </c>
       <c r="AF65" s="4"/>
-      <c r="AG65" s="2" t="s">
-        <v>301</v>
-      </c>
+      <c r="AG65" s="4"/>
       <c r="AH65" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AI65" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="AI65" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ65" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK65" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B66" s="4">
         <v>62</v>
       </c>
@@ -7261,13 +7360,13 @@
         <v>126</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="U66" s="2" t="s">
         <v>242</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7290,20 +7389,21 @@
         <v>91</v>
       </c>
       <c r="AF66" s="4"/>
-      <c r="AG66" s="2" t="s">
-        <v>301</v>
-      </c>
+      <c r="AG66" s="4"/>
       <c r="AH66" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AI66" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="AI66" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ66" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK66" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B67" s="4">
         <v>63</v>
       </c>
@@ -7350,13 +7450,13 @@
         <v>134</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="U67" s="2" t="s">
         <v>243</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7379,20 +7479,21 @@
         <v>92</v>
       </c>
       <c r="AF67" s="4"/>
-      <c r="AG67" s="2" t="s">
-        <v>302</v>
-      </c>
+      <c r="AG67" s="4"/>
       <c r="AH67" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI67" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="AI67" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ67" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK67" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B68" s="4">
         <v>64</v>
       </c>
@@ -7436,13 +7537,13 @@
         <v>126</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>243</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7465,20 +7566,21 @@
         <v>92</v>
       </c>
       <c r="AF68" s="4"/>
-      <c r="AG68" s="2" t="s">
-        <v>302</v>
-      </c>
+      <c r="AG68" s="4"/>
       <c r="AH68" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI68" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="AI68" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="AJ68" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AK68" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7493,8 +7595,9 @@
       <c r="AD69" s="4"/>
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
-    </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG69" s="4"/>
+    </row>
+    <row r="70" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7517,9 +7620,10 @@
       <c r="AD70" s="4"/>
       <c r="AE70" s="4"/>
       <c r="AF70" s="4"/>
-      <c r="AM70" s="4"/>
-    </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG70" s="4"/>
+      <c r="AN70" s="4"/>
+    </row>
+    <row r="71" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7539,9 +7643,10 @@
       <c r="AA71" s="4"/>
       <c r="AE71" s="4"/>
       <c r="AF71" s="4"/>
-      <c r="AM71" s="4"/>
-    </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG71" s="4"/>
+      <c r="AN71" s="4"/>
+    </row>
+    <row r="72" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7561,9 +7666,10 @@
       <c r="AA72" s="4"/>
       <c r="AE72" s="4"/>
       <c r="AF72" s="4"/>
-      <c r="AM72" s="4"/>
-    </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG72" s="4"/>
+      <c r="AN72" s="4"/>
+    </row>
+    <row r="73" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7583,9 +7689,10 @@
       <c r="AA73" s="4"/>
       <c r="AE73" s="4"/>
       <c r="AF73" s="4"/>
-      <c r="AM73" s="4"/>
-    </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG73" s="4"/>
+      <c r="AN73" s="4"/>
+    </row>
+    <row r="74" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7605,9 +7712,10 @@
       <c r="AA74" s="4"/>
       <c r="AE74" s="4"/>
       <c r="AF74" s="4"/>
-      <c r="AM74" s="4"/>
-    </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG74" s="4"/>
+      <c r="AN74" s="4"/>
+    </row>
+    <row r="75" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7627,9 +7735,10 @@
       <c r="AA75" s="4"/>
       <c r="AE75" s="4"/>
       <c r="AF75" s="4"/>
-      <c r="AM75" s="4"/>
-    </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG75" s="4"/>
+      <c r="AN75" s="4"/>
+    </row>
+    <row r="76" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7649,9 +7758,10 @@
       <c r="AA76" s="4"/>
       <c r="AE76" s="4"/>
       <c r="AF76" s="4"/>
-      <c r="AM76" s="4"/>
-    </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG76" s="4"/>
+      <c r="AN76" s="4"/>
+    </row>
+    <row r="77" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7671,9 +7781,10 @@
       <c r="AA77" s="4"/>
       <c r="AE77" s="4"/>
       <c r="AF77" s="4"/>
-      <c r="AM77" s="4"/>
-    </row>
-    <row r="78" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG77" s="4"/>
+      <c r="AN77" s="4"/>
+    </row>
+    <row r="78" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7693,9 +7804,10 @@
       <c r="AA78" s="4"/>
       <c r="AE78" s="4"/>
       <c r="AF78" s="4"/>
-      <c r="AM78" s="4"/>
-    </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG78" s="4"/>
+      <c r="AN78" s="4"/>
+    </row>
+    <row r="79" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7715,9 +7827,10 @@
       <c r="AA79" s="4"/>
       <c r="AE79" s="4"/>
       <c r="AF79" s="4"/>
-      <c r="AM79" s="4"/>
-    </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG79" s="4"/>
+      <c r="AN79" s="4"/>
+    </row>
+    <row r="80" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7737,9 +7850,10 @@
       <c r="AA80" s="4"/>
       <c r="AE80" s="4"/>
       <c r="AF80" s="4"/>
-      <c r="AM80" s="4"/>
-    </row>
-    <row r="81" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG80" s="4"/>
+      <c r="AN80" s="4"/>
+    </row>
+    <row r="81" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7759,9 +7873,10 @@
       <c r="AA81" s="4"/>
       <c r="AE81" s="4"/>
       <c r="AF81" s="4"/>
-      <c r="AM81" s="4"/>
-    </row>
-    <row r="82" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG81" s="4"/>
+      <c r="AN81" s="4"/>
+    </row>
+    <row r="82" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7781,9 +7896,10 @@
       <c r="AA82" s="4"/>
       <c r="AE82" s="4"/>
       <c r="AF82" s="4"/>
-      <c r="AM82" s="4"/>
-    </row>
-    <row r="83" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG82" s="4"/>
+      <c r="AN82" s="4"/>
+    </row>
+    <row r="83" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7803,9 +7919,10 @@
       <c r="AA83" s="4"/>
       <c r="AE83" s="4"/>
       <c r="AF83" s="4"/>
-      <c r="AM83" s="4"/>
-    </row>
-    <row r="84" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG83" s="4"/>
+      <c r="AN83" s="4"/>
+    </row>
+    <row r="84" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -7825,9 +7942,10 @@
       <c r="AA84" s="4"/>
       <c r="AE84" s="4"/>
       <c r="AF84" s="4"/>
-      <c r="AM84" s="4"/>
-    </row>
-    <row r="85" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG84" s="4"/>
+      <c r="AN84" s="4"/>
+    </row>
+    <row r="85" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -7847,9 +7965,10 @@
       <c r="AA85" s="4"/>
       <c r="AE85" s="4"/>
       <c r="AF85" s="4"/>
-      <c r="AM85" s="4"/>
-    </row>
-    <row r="86" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG85" s="4"/>
+      <c r="AN85" s="4"/>
+    </row>
+    <row r="86" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -7869,9 +7988,10 @@
       <c r="AA86" s="4"/>
       <c r="AE86" s="4"/>
       <c r="AF86" s="4"/>
-      <c r="AM86" s="4"/>
-    </row>
-    <row r="87" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG86" s="4"/>
+      <c r="AN86" s="4"/>
+    </row>
+    <row r="87" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -7891,9 +8011,10 @@
       <c r="AA87" s="4"/>
       <c r="AE87" s="4"/>
       <c r="AF87" s="4"/>
-      <c r="AM87" s="4"/>
-    </row>
-    <row r="88" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG87" s="4"/>
+      <c r="AN87" s="4"/>
+    </row>
+    <row r="88" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -7913,9 +8034,10 @@
       <c r="AA88" s="4"/>
       <c r="AE88" s="4"/>
       <c r="AF88" s="4"/>
-      <c r="AM88" s="4"/>
-    </row>
-    <row r="89" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG88" s="4"/>
+      <c r="AN88" s="4"/>
+    </row>
+    <row r="89" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -7935,9 +8057,10 @@
       <c r="AA89" s="4"/>
       <c r="AE89" s="4"/>
       <c r="AF89" s="4"/>
-      <c r="AM89" s="4"/>
-    </row>
-    <row r="90" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG89" s="4"/>
+      <c r="AN89" s="4"/>
+    </row>
+    <row r="90" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -7957,9 +8080,10 @@
       <c r="AA90" s="4"/>
       <c r="AE90" s="4"/>
       <c r="AF90" s="4"/>
-      <c r="AM90" s="4"/>
-    </row>
-    <row r="91" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG90" s="4"/>
+      <c r="AN90" s="4"/>
+    </row>
+    <row r="91" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -7979,9 +8103,10 @@
       <c r="AA91" s="4"/>
       <c r="AE91" s="4"/>
       <c r="AF91" s="4"/>
-      <c r="AM91" s="4"/>
-    </row>
-    <row r="92" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG91" s="4"/>
+      <c r="AN91" s="4"/>
+    </row>
+    <row r="92" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -8001,9 +8126,10 @@
       <c r="AA92" s="4"/>
       <c r="AE92" s="4"/>
       <c r="AF92" s="4"/>
-      <c r="AM92" s="4"/>
-    </row>
-    <row r="93" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG92" s="4"/>
+      <c r="AN92" s="4"/>
+    </row>
+    <row r="93" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -8014,9 +8140,10 @@
       <c r="AA93" s="4"/>
       <c r="AE93" s="4"/>
       <c r="AF93" s="4"/>
-      <c r="AM93" s="4"/>
-    </row>
-    <row r="94" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG93" s="4"/>
+      <c r="AN93" s="4"/>
+    </row>
+    <row r="94" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -8033,9 +8160,10 @@
       <c r="AA94" s="4"/>
       <c r="AE94" s="4"/>
       <c r="AF94" s="4"/>
-      <c r="AM94" s="4"/>
-    </row>
-    <row r="95" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG94" s="4"/>
+      <c r="AN94" s="4"/>
+    </row>
+    <row r="95" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -8052,9 +8180,10 @@
       <c r="AA95" s="4"/>
       <c r="AE95" s="4"/>
       <c r="AF95" s="4"/>
-      <c r="AM95" s="4"/>
-    </row>
-    <row r="96" spans="2:39" x14ac:dyDescent="0.15">
+      <c r="AG95" s="4"/>
+      <c r="AN95" s="4"/>
+    </row>
+    <row r="96" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -8071,9 +8200,10 @@
       <c r="AA96" s="4"/>
       <c r="AE96" s="4"/>
       <c r="AF96" s="4"/>
-      <c r="AM96" s="4"/>
-    </row>
-    <row r="97" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG96" s="4"/>
+      <c r="AN96" s="4"/>
+    </row>
+    <row r="97" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -8090,9 +8220,10 @@
       <c r="AA97" s="4"/>
       <c r="AE97" s="4"/>
       <c r="AF97" s="4"/>
-      <c r="AM97" s="4"/>
-    </row>
-    <row r="98" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG97" s="4"/>
+      <c r="AN97" s="4"/>
+    </row>
+    <row r="98" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -8109,9 +8240,10 @@
       <c r="AA98" s="4"/>
       <c r="AE98" s="4"/>
       <c r="AF98" s="4"/>
-      <c r="AM98" s="4"/>
-    </row>
-    <row r="99" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG98" s="4"/>
+      <c r="AN98" s="4"/>
+    </row>
+    <row r="99" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -8128,9 +8260,10 @@
       <c r="AA99" s="4"/>
       <c r="AE99" s="4"/>
       <c r="AF99" s="4"/>
-      <c r="AM99" s="4"/>
-    </row>
-    <row r="100" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG99" s="4"/>
+      <c r="AN99" s="4"/>
+    </row>
+    <row r="100" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -8147,9 +8280,10 @@
       <c r="AA100" s="4"/>
       <c r="AE100" s="4"/>
       <c r="AF100" s="4"/>
-      <c r="AM100" s="4"/>
-    </row>
-    <row r="101" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG100" s="4"/>
+      <c r="AN100" s="4"/>
+    </row>
+    <row r="101" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -8166,9 +8300,10 @@
       <c r="AA101" s="4"/>
       <c r="AE101" s="4"/>
       <c r="AF101" s="4"/>
-      <c r="AM101" s="4"/>
-    </row>
-    <row r="102" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG101" s="4"/>
+      <c r="AN101" s="4"/>
+    </row>
+    <row r="102" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -8185,9 +8320,10 @@
       <c r="AA102" s="4"/>
       <c r="AE102" s="4"/>
       <c r="AF102" s="4"/>
-      <c r="AM102" s="4"/>
-    </row>
-    <row r="103" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG102" s="4"/>
+      <c r="AN102" s="4"/>
+    </row>
+    <row r="103" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -8197,8 +8333,9 @@
       <c r="AA103" s="4"/>
       <c r="AE103" s="4"/>
       <c r="AF103" s="4"/>
-    </row>
-    <row r="104" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG103" s="4"/>
+    </row>
+    <row r="104" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -8208,8 +8345,9 @@
       <c r="AA104" s="4"/>
       <c r="AE104" s="4"/>
       <c r="AF104" s="4"/>
-    </row>
-    <row r="105" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG104" s="4"/>
+    </row>
+    <row r="105" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -8219,8 +8357,9 @@
       <c r="AA105" s="4"/>
       <c r="AE105" s="4"/>
       <c r="AF105" s="4"/>
-    </row>
-    <row r="106" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG105" s="4"/>
+    </row>
+    <row r="106" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -8230,8 +8369,9 @@
       <c r="AA106" s="4"/>
       <c r="AE106" s="4"/>
       <c r="AF106" s="4"/>
-    </row>
-    <row r="107" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG106" s="4"/>
+    </row>
+    <row r="107" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -8241,8 +8381,9 @@
       <c r="AA107" s="4"/>
       <c r="AE107" s="4"/>
       <c r="AF107" s="4"/>
-    </row>
-    <row r="108" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG107" s="4"/>
+    </row>
+    <row r="108" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8252,8 +8393,9 @@
       <c r="AA108" s="4"/>
       <c r="AE108" s="4"/>
       <c r="AF108" s="4"/>
-    </row>
-    <row r="109" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG108" s="4"/>
+    </row>
+    <row r="109" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8263,8 +8405,9 @@
       <c r="AA109" s="4"/>
       <c r="AE109" s="4"/>
       <c r="AF109" s="4"/>
-    </row>
-    <row r="110" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG109" s="4"/>
+    </row>
+    <row r="110" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8274,8 +8417,9 @@
       <c r="AA110" s="4"/>
       <c r="AE110" s="4"/>
       <c r="AF110" s="4"/>
-    </row>
-    <row r="111" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG110" s="4"/>
+    </row>
+    <row r="111" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8285,8 +8429,9 @@
       <c r="AA111" s="4"/>
       <c r="AE111" s="4"/>
       <c r="AF111" s="4"/>
-    </row>
-    <row r="112" spans="5:39" x14ac:dyDescent="0.15">
+      <c r="AG111" s="4"/>
+    </row>
+    <row r="112" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8296,8 +8441,9 @@
       <c r="AA112" s="4"/>
       <c r="AE112" s="4"/>
       <c r="AF112" s="4"/>
-    </row>
-    <row r="113" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG112" s="4"/>
+    </row>
+    <row r="113" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8307,8 +8453,9 @@
       <c r="AA113" s="4"/>
       <c r="AE113" s="4"/>
       <c r="AF113" s="4"/>
-    </row>
-    <row r="114" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG113" s="4"/>
+    </row>
+    <row r="114" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8318,8 +8465,9 @@
       <c r="AA114" s="4"/>
       <c r="AE114" s="4"/>
       <c r="AF114" s="4"/>
-    </row>
-    <row r="115" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG114" s="4"/>
+    </row>
+    <row r="115" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8329,8 +8477,9 @@
       <c r="AA115" s="4"/>
       <c r="AE115" s="4"/>
       <c r="AF115" s="4"/>
-    </row>
-    <row r="116" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG115" s="4"/>
+    </row>
+    <row r="116" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8340,8 +8489,9 @@
       <c r="AA116" s="4"/>
       <c r="AE116" s="4"/>
       <c r="AF116" s="4"/>
-    </row>
-    <row r="117" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG116" s="4"/>
+    </row>
+    <row r="117" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8351,8 +8501,9 @@
       <c r="AA117" s="4"/>
       <c r="AE117" s="4"/>
       <c r="AF117" s="4"/>
-    </row>
-    <row r="118" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG117" s="4"/>
+    </row>
+    <row r="118" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8362,8 +8513,9 @@
       <c r="AA118" s="4"/>
       <c r="AE118" s="4"/>
       <c r="AF118" s="4"/>
-    </row>
-    <row r="119" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG118" s="4"/>
+    </row>
+    <row r="119" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8373,8 +8525,9 @@
       <c r="AA119" s="4"/>
       <c r="AE119" s="4"/>
       <c r="AF119" s="4"/>
-    </row>
-    <row r="120" spans="5:32" x14ac:dyDescent="0.15">
+      <c r="AG119" s="4"/>
+    </row>
+    <row r="120" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>
@@ -8384,6 +8537,7 @@
       <c r="AA120" s="4"/>
       <c r="AE120" s="4"/>
       <c r="AF120" s="4"/>
+      <c r="AG120" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCC11B7-82B1-4486-AC51-FFB38DFCED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7900C-39E1-4BFE-A844-F9FABD91A998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="1110" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="329">
   <si>
     <t>0</t>
   </si>
@@ -1218,6 +1218,22 @@
   </si>
   <si>
     <t>Assets/Model/Prefab/4485.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/tulei_p.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/tulei_building.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/tulei_broken.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"BuildingAddTroopMorale", value:10, bound:2, tartgetType:0}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1721,36 +1737,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AO120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.5" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.453125" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.125" style="2" customWidth="1"/>
-    <col min="31" max="33" width="71.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="37.875" style="2" customWidth="1"/>
-    <col min="37" max="37" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="164.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.26953125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.08984375" style="2" customWidth="1"/>
+    <col min="31" max="33" width="71.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="37.90625" style="2" customWidth="1"/>
+    <col min="37" max="37" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="164.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1859,7 +1875,7 @@
       <c r="AN1" s="9"/>
       <c r="AO1" s="7"/>
     </row>
-    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1904,7 +1920,7 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
     </row>
-    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -2021,7 +2037,7 @@
       <c r="AN3" s="8"/>
       <c r="AO3" s="8"/>
     </row>
-    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2137,7 +2153,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2214,7 +2230,7 @@
       <c r="AH5" s="4"/>
       <c r="AN5" s="4"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2292,7 +2308,7 @@
       <c r="AH6" s="4"/>
       <c r="AN6" s="4"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -2369,7 +2385,7 @@
       <c r="AH7" s="4"/>
       <c r="AN7" s="4"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>121</v>
       </c>
@@ -2461,7 +2477,7 @@
       </c>
       <c r="AN8" s="4"/>
     </row>
-    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2550,7 +2566,7 @@
       </c>
       <c r="AN9" s="4"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2639,7 +2655,7 @@
       </c>
       <c r="AN10" s="4"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2725,7 +2741,7 @@
       </c>
       <c r="AN11" s="4"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2811,7 +2827,7 @@
       </c>
       <c r="AN12" s="4"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2883,17 +2899,17 @@
         <v>279</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>130</v>
+        <v>325</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>212</v>
+        <v>326</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="AN13" s="4"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2965,17 +2981,17 @@
         <v>280</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>130</v>
+        <v>325</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>212</v>
+        <v>326</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="AN14" s="4"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -3061,7 +3077,7 @@
       </c>
       <c r="AN15" s="4"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3147,7 +3163,7 @@
       </c>
       <c r="AN16" s="4"/>
     </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3231,9 +3247,12 @@
       <c r="AK17" s="2" t="s">
         <v>318</v>
       </c>
+      <c r="AL17" s="2" t="s">
+        <v>328</v>
+      </c>
       <c r="AN17" s="4"/>
     </row>
-    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3319,7 +3338,7 @@
       </c>
       <c r="AN18" s="4"/>
     </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -3397,7 +3416,7 @@
       </c>
       <c r="AN19" s="4"/>
     </row>
-    <row r="20" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3475,7 +3494,7 @@
       </c>
       <c r="AN20" s="4"/>
     </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -3557,7 +3576,7 @@
       </c>
       <c r="AN21" s="4"/>
     </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -3639,7 +3658,7 @@
       </c>
       <c r="AN22" s="4"/>
     </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3721,7 +3740,7 @@
       </c>
       <c r="AN23" s="4"/>
     </row>
-    <row r="24" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3803,7 +3822,7 @@
       </c>
       <c r="AN24" s="4"/>
     </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3885,7 +3904,7 @@
       </c>
       <c r="AN25" s="4"/>
     </row>
-    <row r="26" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3967,7 +3986,7 @@
       </c>
       <c r="AN26" s="4"/>
     </row>
-    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -4049,7 +4068,7 @@
       </c>
       <c r="AN27" s="4"/>
     </row>
-    <row r="28" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -4127,7 +4146,7 @@
       </c>
       <c r="AN28" s="4"/>
     </row>
-    <row r="29" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -4205,7 +4224,7 @@
       </c>
       <c r="AN29" s="4"/>
     </row>
-    <row r="30" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4281,7 +4300,7 @@
       </c>
       <c r="AN30" s="4"/>
     </row>
-    <row r="31" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4359,7 +4378,7 @@
       </c>
       <c r="AN31" s="4"/>
     </row>
-    <row r="32" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4435,7 +4454,7 @@
       </c>
       <c r="AN32" s="4"/>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4513,7 +4532,7 @@
       </c>
       <c r="AN33" s="4"/>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4591,7 +4610,7 @@
       </c>
       <c r="AN34" s="4"/>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4675,7 +4694,7 @@
       </c>
       <c r="AN35" s="4"/>
     </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
         <v>32</v>
       </c>
@@ -4767,7 +4786,7 @@
       </c>
       <c r="AN36" s="4"/>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -4859,7 +4878,7 @@
       </c>
       <c r="AN37" s="4"/>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>34</v>
       </c>
@@ -4948,7 +4967,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -5040,7 +5059,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B40" s="4">
         <v>36</v>
       </c>
@@ -5132,7 +5151,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>37</v>
       </c>
@@ -5224,7 +5243,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B42" s="4">
         <v>38</v>
       </c>
@@ -5316,7 +5335,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5404,7 +5423,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B44" s="4">
         <v>40</v>
       </c>
@@ -5492,7 +5511,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5577,7 +5596,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B46" s="4">
         <v>42</v>
       </c>
@@ -5668,7 +5687,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5756,7 +5775,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5841,7 +5860,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -5926,7 +5945,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B50" s="4">
         <v>46</v>
       </c>
@@ -6014,7 +6033,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -6102,7 +6121,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -6190,7 +6209,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -6271,7 +6290,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -6362,7 +6381,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6446,7 +6465,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6527,7 +6546,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="57" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6611,7 +6630,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="58" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6692,7 +6711,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6782,7 +6801,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="60" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6869,7 +6888,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -6959,7 +6978,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -7046,7 +7065,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -7137,7 +7156,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -7226,7 +7245,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
         <v>61</v>
       </c>
@@ -7316,7 +7335,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
         <v>62</v>
       </c>
@@ -7403,7 +7422,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
         <v>63</v>
       </c>
@@ -7493,7 +7512,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B68" s="4">
         <v>64</v>
       </c>
@@ -7580,7 +7599,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7597,7 +7616,7 @@
       <c r="AF69" s="4"/>
       <c r="AG69" s="4"/>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7623,7 +7642,7 @@
       <c r="AG70" s="4"/>
       <c r="AN70" s="4"/>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7646,7 +7665,7 @@
       <c r="AG71" s="4"/>
       <c r="AN71" s="4"/>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7669,7 +7688,7 @@
       <c r="AG72" s="4"/>
       <c r="AN72" s="4"/>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7692,7 +7711,7 @@
       <c r="AG73" s="4"/>
       <c r="AN73" s="4"/>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7715,7 +7734,7 @@
       <c r="AG74" s="4"/>
       <c r="AN74" s="4"/>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7738,7 +7757,7 @@
       <c r="AG75" s="4"/>
       <c r="AN75" s="4"/>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7761,7 +7780,7 @@
       <c r="AG76" s="4"/>
       <c r="AN76" s="4"/>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7784,7 +7803,7 @@
       <c r="AG77" s="4"/>
       <c r="AN77" s="4"/>
     </row>
-    <row r="78" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7807,7 +7826,7 @@
       <c r="AG78" s="4"/>
       <c r="AN78" s="4"/>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7830,7 +7849,7 @@
       <c r="AG79" s="4"/>
       <c r="AN79" s="4"/>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7853,7 +7872,7 @@
       <c r="AG80" s="4"/>
       <c r="AN80" s="4"/>
     </row>
-    <row r="81" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7876,7 +7895,7 @@
       <c r="AG81" s="4"/>
       <c r="AN81" s="4"/>
     </row>
-    <row r="82" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7899,7 +7918,7 @@
       <c r="AG82" s="4"/>
       <c r="AN82" s="4"/>
     </row>
-    <row r="83" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7922,7 +7941,7 @@
       <c r="AG83" s="4"/>
       <c r="AN83" s="4"/>
     </row>
-    <row r="84" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -7945,7 +7964,7 @@
       <c r="AG84" s="4"/>
       <c r="AN84" s="4"/>
     </row>
-    <row r="85" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -7968,7 +7987,7 @@
       <c r="AG85" s="4"/>
       <c r="AN85" s="4"/>
     </row>
-    <row r="86" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -7991,7 +8010,7 @@
       <c r="AG86" s="4"/>
       <c r="AN86" s="4"/>
     </row>
-    <row r="87" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -8014,7 +8033,7 @@
       <c r="AG87" s="4"/>
       <c r="AN87" s="4"/>
     </row>
-    <row r="88" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -8037,7 +8056,7 @@
       <c r="AG88" s="4"/>
       <c r="AN88" s="4"/>
     </row>
-    <row r="89" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -8060,7 +8079,7 @@
       <c r="AG89" s="4"/>
       <c r="AN89" s="4"/>
     </row>
-    <row r="90" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8083,7 +8102,7 @@
       <c r="AG90" s="4"/>
       <c r="AN90" s="4"/>
     </row>
-    <row r="91" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -8106,7 +8125,7 @@
       <c r="AG91" s="4"/>
       <c r="AN91" s="4"/>
     </row>
-    <row r="92" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -8129,7 +8148,7 @@
       <c r="AG92" s="4"/>
       <c r="AN92" s="4"/>
     </row>
-    <row r="93" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -8143,7 +8162,7 @@
       <c r="AG93" s="4"/>
       <c r="AN93" s="4"/>
     </row>
-    <row r="94" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:40" x14ac:dyDescent="0.25">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -8163,7 +8182,7 @@
       <c r="AG94" s="4"/>
       <c r="AN94" s="4"/>
     </row>
-    <row r="95" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:40" x14ac:dyDescent="0.25">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -8183,7 +8202,7 @@
       <c r="AG95" s="4"/>
       <c r="AN95" s="4"/>
     </row>
-    <row r="96" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:40" x14ac:dyDescent="0.25">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -8203,7 +8222,7 @@
       <c r="AG96" s="4"/>
       <c r="AN96" s="4"/>
     </row>
-    <row r="97" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="97" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -8223,7 +8242,7 @@
       <c r="AG97" s="4"/>
       <c r="AN97" s="4"/>
     </row>
-    <row r="98" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="98" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -8243,7 +8262,7 @@
       <c r="AG98" s="4"/>
       <c r="AN98" s="4"/>
     </row>
-    <row r="99" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="99" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -8263,7 +8282,7 @@
       <c r="AG99" s="4"/>
       <c r="AN99" s="4"/>
     </row>
-    <row r="100" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="100" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -8283,7 +8302,7 @@
       <c r="AG100" s="4"/>
       <c r="AN100" s="4"/>
     </row>
-    <row r="101" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="101" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -8303,7 +8322,7 @@
       <c r="AG101" s="4"/>
       <c r="AN101" s="4"/>
     </row>
-    <row r="102" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="102" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -8323,7 +8342,7 @@
       <c r="AG102" s="4"/>
       <c r="AN102" s="4"/>
     </row>
-    <row r="103" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="103" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -8335,7 +8354,7 @@
       <c r="AF103" s="4"/>
       <c r="AG103" s="4"/>
     </row>
-    <row r="104" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="104" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -8347,7 +8366,7 @@
       <c r="AF104" s="4"/>
       <c r="AG104" s="4"/>
     </row>
-    <row r="105" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="105" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -8359,7 +8378,7 @@
       <c r="AF105" s="4"/>
       <c r="AG105" s="4"/>
     </row>
-    <row r="106" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="106" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -8371,7 +8390,7 @@
       <c r="AF106" s="4"/>
       <c r="AG106" s="4"/>
     </row>
-    <row r="107" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="107" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -8383,7 +8402,7 @@
       <c r="AF107" s="4"/>
       <c r="AG107" s="4"/>
     </row>
-    <row r="108" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="108" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8395,7 +8414,7 @@
       <c r="AF108" s="4"/>
       <c r="AG108" s="4"/>
     </row>
-    <row r="109" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="109" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8407,7 +8426,7 @@
       <c r="AF109" s="4"/>
       <c r="AG109" s="4"/>
     </row>
-    <row r="110" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="110" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8419,7 +8438,7 @@
       <c r="AF110" s="4"/>
       <c r="AG110" s="4"/>
     </row>
-    <row r="111" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="111" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8431,7 +8450,7 @@
       <c r="AF111" s="4"/>
       <c r="AG111" s="4"/>
     </row>
-    <row r="112" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="112" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8443,7 +8462,7 @@
       <c r="AF112" s="4"/>
       <c r="AG112" s="4"/>
     </row>
-    <row r="113" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8455,7 +8474,7 @@
       <c r="AF113" s="4"/>
       <c r="AG113" s="4"/>
     </row>
-    <row r="114" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8467,7 +8486,7 @@
       <c r="AF114" s="4"/>
       <c r="AG114" s="4"/>
     </row>
-    <row r="115" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8479,7 +8498,7 @@
       <c r="AF115" s="4"/>
       <c r="AG115" s="4"/>
     </row>
-    <row r="116" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8491,7 +8510,7 @@
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
     </row>
-    <row r="117" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8503,7 +8522,7 @@
       <c r="AF117" s="4"/>
       <c r="AG117" s="4"/>
     </row>
-    <row r="118" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8515,7 +8534,7 @@
       <c r="AF118" s="4"/>
       <c r="AG118" s="4"/>
     </row>
-    <row r="119" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8527,7 +8546,7 @@
       <c r="AF119" s="4"/>
       <c r="AG119" s="4"/>
     </row>
-    <row r="120" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7900C-39E1-4BFE-A844-F9FABD91A998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7872FED-0AB0-48E7-B4E7-DCBC4EB86D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="2805" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="343">
   <si>
     <t>0</t>
   </si>
@@ -278,17 +278,10 @@
     <t>阻碍部队行进的障碍物</t>
   </si>
   <si>
-    <t>阻碍部队行进的障碍物，比土垒坚固</t>
-  </si>
-  <si>
     <t>每回合对位于周围２～３区格内的敌方部队执行投石攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>强化周围３区格内己方部队之攻击力，并提升单挑成功率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回复位于周围２区格内的己方部队之气力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -806,10 +799,6 @@
   </si>
   <si>
     <t>Assets/Model/Prefab/4447.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Model/Prefab/4479.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1217,10 +1206,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Model/Prefab/4485.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Model/Prefab/tulei_p.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1229,11 +1214,83 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Model/Prefab/tulei_broken.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"BuildingAddTroopMorale", value:10, bound:2, tartgetType:0}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/junyuetai.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/junyuetai_create.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/junyuetai_broken.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/taigutai.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/taigutai_create.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/taigutai_broken.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/toushitai.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/toushitai_broken.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/wall.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/wall_building.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/lianlulou.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4304.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4284.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4294.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4310.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/4312.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"BuildingImproveTroopAttack", value:10, bound:3, tartgetType:0},{class:"BuildingImproveTroopAttack", value:-10, bound:3, tartgetType:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阻碍部队行进的障碍物，比土垒坚固</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周围３区格内己方部队攻击力+10，敌方部队攻击力-10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1737,36 +1794,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AO120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.08984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.7265625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.453125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.5" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.26953125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.08984375" style="2" customWidth="1"/>
-    <col min="31" max="33" width="71.90625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="37.90625" style="2" customWidth="1"/>
-    <col min="37" max="37" width="37.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="164.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.125" style="2" customWidth="1"/>
+    <col min="31" max="33" width="71.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="37.875" style="2" customWidth="1"/>
+    <col min="37" max="37" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="164.75" style="2" bestFit="1" customWidth="1"/>
     <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1776,87 +1833,87 @@
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G1" s="14"/>
       <c r="H1" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>54</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Z1" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AA1" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AB1" s="18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AC1" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AF1" s="14"/>
       <c r="AG1" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH1" s="9" t="s">
         <v>53</v>
@@ -1875,7 +1932,7 @@
       <c r="AN1" s="9"/>
       <c r="AO1" s="7"/>
     </row>
-    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1920,7 +1977,7 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
     </row>
-    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1931,113 +1988,113 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>55</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AE3" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG3" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AJ3" s="13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AK3" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AL3" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AM3" s="8"/>
       <c r="AN3" s="8"/>
       <c r="AO3" s="8"/>
     </row>
-    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2048,10 +2105,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>8</v>
@@ -2063,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J4" s="15" t="s">
         <v>8</v>
@@ -2081,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>6</v>
@@ -2099,16 +2156,16 @@
         <v>8</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2117,10 +2174,10 @@
         <v>6</v>
       </c>
       <c r="AA4" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AC4" s="15" t="s">
         <v>8</v>
@@ -2150,10 +2207,10 @@
         <v>5</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2171,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -2180,16 +2237,16 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -2214,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC5" s="4">
         <v>250</v>
@@ -2230,7 +2287,7 @@
       <c r="AH5" s="4"/>
       <c r="AN5" s="4"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2249,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -2258,16 +2315,16 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
@@ -2292,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC6" s="4">
         <v>100</v>
@@ -2308,12 +2365,12 @@
       <c r="AH6" s="4"/>
       <c r="AN6" s="4"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -2326,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -2335,16 +2392,16 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
@@ -2369,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC7" s="4">
         <v>50</v>
@@ -2378,22 +2435,22 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AN7" s="4"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2406,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -2415,16 +2472,16 @@
         <v>1500</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6">
@@ -2447,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC8" s="4">
         <v>0</v>
@@ -2461,28 +2518,28 @@
       <c r="AF8" s="4"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>130</v>
+        <v>335</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>212</v>
+        <v>336</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>212</v>
+        <v>337</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AN8" s="4"/>
     </row>
-    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2495,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J9" s="4">
         <v>26</v>
@@ -2504,16 +2561,16 @@
         <v>2000</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6">
@@ -2536,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC9" s="4">
         <v>0</v>
@@ -2545,33 +2602,33 @@
         <v>0</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>130</v>
+        <v>338</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>212</v>
+        <v>336</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>212</v>
+        <v>337</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN9" s="4"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2584,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J10" s="4">
         <v>27</v>
@@ -2593,16 +2650,16 @@
         <v>2500</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
@@ -2625,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC10" s="4">
         <v>0</v>
@@ -2639,28 +2696,28 @@
       <c r="AF10" s="4"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>130</v>
+        <v>339</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>212</v>
+        <v>336</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>212</v>
+        <v>337</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AN10" s="4"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2673,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
@@ -2685,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6">
@@ -2714,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC11" s="4">
         <v>0</v>
@@ -2728,20 +2785,20 @@
       <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN11" s="4"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2759,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J12" s="4">
         <v>26</v>
@@ -2771,13 +2828,13 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6">
@@ -2800,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC12" s="4">
         <v>0</v>
@@ -2814,25 +2871,25 @@
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>214</v>
+        <v>334</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN12" s="4"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D13" s="4">
         <v>2</v>
@@ -2845,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J13" s="4">
         <v>0</v>
@@ -2863,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -2884,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC13" s="4">
         <v>0</v>
@@ -2896,20 +2953,20 @@
       <c r="AF13" s="4"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AN13" s="4"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2927,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J14" s="4">
         <v>22</v>
@@ -2945,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -2966,32 +3023,32 @@
         <v>0</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC14" s="4">
         <v>0</v>
       </c>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4" t="s">
-        <v>65</v>
+        <v>341</v>
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AN14" s="4"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -3009,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J15" s="4">
         <v>23</v>
@@ -3021,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
@@ -3050,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC15" s="4">
         <v>0</v>
@@ -3059,25 +3116,25 @@
         <v>2</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>213</v>
+        <v>331</v>
       </c>
       <c r="AK15" s="2" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="AN15" s="4"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3095,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J16" s="4">
         <v>0</v>
@@ -3110,10 +3167,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
@@ -3136,34 +3193,37 @@
         <v>0</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC16" s="4">
         <v>0</v>
       </c>
       <c r="AD16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>67</v>
+        <v>342</v>
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>130</v>
+        <v>327</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>212</v>
+        <v>328</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>318</v>
+        <v>329</v>
+      </c>
+      <c r="AL16" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="AN16" s="4"/>
     </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3181,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>
@@ -3196,10 +3256,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6">
@@ -3222,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC17" s="4">
         <v>0</v>
@@ -3231,28 +3291,28 @@
         <v>2</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>130</v>
+        <v>324</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>212</v>
+        <v>325</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AL17" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN17" s="4"/>
     </row>
-    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3270,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J18" s="4">
         <v>22</v>
@@ -3288,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6">
@@ -3311,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC18" s="4">
         <v>0</v>
@@ -3320,30 +3380,30 @@
         <v>2</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AF18" s="4"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AK18" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN18" s="4"/>
     </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -3356,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J19" s="4">
         <v>0</v>
@@ -3374,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -3393,30 +3453,30 @@
         <v>0</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC19" s="4">
         <v>0</v>
       </c>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AF19" s="4"/>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN19" s="4"/>
     </row>
-    <row r="20" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3434,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J20" s="4">
         <v>0</v>
@@ -3452,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -3471,35 +3531,35 @@
         <v>0</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC20" s="4">
         <v>0</v>
       </c>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AF20" s="4"/>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN20" s="4"/>
     </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D21" s="4">
         <v>3</v>
@@ -3512,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J21" s="4">
         <v>0</v>
@@ -3530,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
@@ -3551,37 +3611,37 @@
         <v>0</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC21" s="4">
         <v>0</v>
       </c>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AF21" s="4"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN21" s="4"/>
     </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -3594,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J22" s="4">
         <v>31</v>
@@ -3612,7 +3672,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -3633,32 +3693,32 @@
         <v>0</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC22" s="4">
         <v>0</v>
       </c>
       <c r="AD22" s="4"/>
       <c r="AE22" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN22" s="4"/>
     </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3676,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J23" s="4">
         <v>0</v>
@@ -3694,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
@@ -3715,32 +3775,32 @@
         <v>0</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC23" s="4">
         <v>0</v>
       </c>
       <c r="AD23" s="4"/>
       <c r="AE23" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK23" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN23" s="4"/>
     </row>
-    <row r="24" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3758,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J24" s="4">
         <v>31</v>
@@ -3776,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
@@ -3797,32 +3857,32 @@
         <v>0</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC24" s="4">
         <v>0</v>
       </c>
       <c r="AD24" s="4"/>
       <c r="AE24" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AF24" s="4"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN24" s="4"/>
     </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3840,7 +3900,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J25" s="4">
         <v>0</v>
@@ -3858,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -3879,32 +3939,32 @@
         <v>0</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC25" s="4">
         <v>0</v>
       </c>
       <c r="AD25" s="4"/>
       <c r="AE25" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF25" s="4"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN25" s="4"/>
     </row>
-    <row r="26" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3922,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J26" s="4">
         <v>32</v>
@@ -3940,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
@@ -3961,37 +4021,37 @@
         <v>0</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC26" s="4">
         <v>0</v>
       </c>
       <c r="AD26" s="4"/>
       <c r="AE26" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AF26" s="4"/>
       <c r="AG26" s="4"/>
       <c r="AH26" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN26" s="4"/>
     </row>
-    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
@@ -4004,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J27" s="4">
         <v>32</v>
@@ -4022,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
@@ -4043,32 +4103,32 @@
         <v>0</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC27" s="4">
         <v>0</v>
       </c>
       <c r="AD27" s="4"/>
       <c r="AE27" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF27" s="4"/>
       <c r="AG27" s="4"/>
       <c r="AH27" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK27" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN27" s="4"/>
     </row>
-    <row r="28" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -4086,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J28" s="4">
         <v>0</v>
@@ -4104,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
@@ -4123,30 +4183,30 @@
         <v>0</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC28" s="4">
         <v>0</v>
       </c>
       <c r="AD28" s="4"/>
       <c r="AE28" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AF28" s="4"/>
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
       <c r="AI28" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN28" s="4"/>
     </row>
-    <row r="29" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -4164,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J29" s="4">
         <v>0</v>
@@ -4182,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
@@ -4201,30 +4261,30 @@
         <v>0</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC29" s="4">
         <v>0</v>
       </c>
       <c r="AD29" s="4"/>
       <c r="AE29" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF29" s="4"/>
       <c r="AG29" s="4"/>
       <c r="AH29" s="4"/>
       <c r="AI29" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN29" s="4"/>
     </row>
-    <row r="30" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4242,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J30" s="4">
         <v>0</v>
@@ -4258,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
@@ -4277,30 +4337,30 @@
         <v>0</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC30" s="4">
         <v>0</v>
       </c>
       <c r="AD30" s="4"/>
       <c r="AE30" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF30" s="4"/>
       <c r="AG30" s="4"/>
       <c r="AH30" s="4"/>
       <c r="AI30" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK30" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN30" s="4"/>
     </row>
-    <row r="31" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4318,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J31" s="4">
         <v>0</v>
@@ -4336,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="6"/>
@@ -4355,30 +4415,30 @@
         <v>0</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC31" s="4">
         <v>0</v>
       </c>
       <c r="AD31" s="4"/>
       <c r="AE31" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AF31" s="4"/>
       <c r="AG31" s="4"/>
       <c r="AH31" s="4"/>
       <c r="AI31" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN31" s="4"/>
     </row>
-    <row r="32" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4396,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J32" s="4">
         <v>0</v>
@@ -4412,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
@@ -4431,30 +4491,30 @@
         <v>0</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC32" s="4">
         <v>0</v>
       </c>
       <c r="AD32" s="4"/>
       <c r="AE32" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AF32" s="4"/>
       <c r="AG32" s="4"/>
       <c r="AH32" s="4"/>
       <c r="AI32" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK32" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN32" s="4"/>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4472,7 +4532,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J33" s="4">
         <v>0</v>
@@ -4490,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
@@ -4509,30 +4569,30 @@
         <v>0</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC33" s="4">
         <v>0</v>
       </c>
       <c r="AD33" s="4"/>
       <c r="AE33" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF33" s="4"/>
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
       <c r="AI33" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK33" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN33" s="4"/>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4550,7 +4610,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J34" s="4">
         <v>0</v>
@@ -4568,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
@@ -4587,30 +4647,30 @@
         <v>0</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC34" s="4">
         <v>0</v>
       </c>
       <c r="AD34" s="4"/>
       <c r="AE34" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF34" s="4"/>
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>
       <c r="AI34" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK34" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN34" s="4"/>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4628,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J35" s="4">
         <v>0</v>
@@ -4646,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
@@ -4667,39 +4727,39 @@
         <v>0</v>
       </c>
       <c r="AB35" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC35" s="4">
         <v>100</v>
       </c>
       <c r="AD35" s="4"/>
       <c r="AE35" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF35" s="4"/>
       <c r="AG35" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AK35" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN35" s="4"/>
     </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B36" s="4">
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4714,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J36" s="4">
         <v>0</v>
@@ -4732,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="6">
@@ -4757,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="AB36" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC36" s="4">
         <v>30</v>
@@ -4766,32 +4826,32 @@
         <v>3</v>
       </c>
       <c r="AE36" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AF36" s="4"/>
       <c r="AG36" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AH36" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI36" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AH36" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AI36" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="AJ36" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AK36" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AN36" s="4"/>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B37" s="4">
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4806,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J37" s="4">
         <v>0</v>
@@ -4824,7 +4884,7 @@
         <v>1</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="6">
@@ -4849,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC37" s="4">
         <v>30</v>
@@ -4858,32 +4918,32 @@
         <v>3</v>
       </c>
       <c r="AE37" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AF37" s="4"/>
       <c r="AG37" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AK37" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AN37" s="4"/>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B38" s="4">
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4892,13 +4952,13 @@
         <v>34</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H38" s="4">
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J38" s="4">
         <v>0</v>
@@ -4916,19 +4976,19 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4939,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC38" s="4">
         <v>30</v>
@@ -4948,31 +5008,31 @@
         <v>4</v>
       </c>
       <c r="AE38" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AF38" s="4"/>
       <c r="AG38" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK38" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="39" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B39" s="4">
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -4981,13 +5041,13 @@
         <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H39" s="4">
         <v>1</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J39" s="4">
         <v>0</v>
@@ -5005,22 +5065,22 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -5031,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC39" s="4">
         <v>30</v>
@@ -5040,31 +5100,31 @@
         <v>2</v>
       </c>
       <c r="AE39" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AF39" s="4"/>
       <c r="AG39" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK39" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B40" s="4">
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -5073,13 +5133,13 @@
         <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H40" s="4">
         <v>1</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J40" s="4">
         <v>0</v>
@@ -5097,22 +5157,22 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -5123,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC40" s="4">
         <v>30</v>
@@ -5132,31 +5192,31 @@
         <v>2</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AF40" s="4"/>
       <c r="AG40" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK40" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B41" s="4">
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -5165,13 +5225,13 @@
         <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H41" s="4">
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J41" s="4">
         <v>0</v>
@@ -5189,22 +5249,22 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -5215,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC41" s="4">
         <v>30</v>
@@ -5224,31 +5284,31 @@
         <v>2</v>
       </c>
       <c r="AE41" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF41" s="4"/>
       <c r="AG41" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK41" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B42" s="4">
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -5257,13 +5317,13 @@
         <v>38</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H42" s="4">
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J42" s="4">
         <v>0</v>
@@ -5281,22 +5341,22 @@
         <v>0</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5307,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC42" s="4">
         <v>30</v>
@@ -5316,26 +5376,26 @@
         <v>2</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF42" s="4"/>
       <c r="AG42" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK42" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5352,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J43" s="4">
         <v>0</v>
@@ -5370,16 +5430,16 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
@@ -5390,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC43" s="4">
         <v>30</v>
@@ -5399,36 +5459,36 @@
         <v>3</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AF43" s="4">
         <v>1</v>
       </c>
       <c r="AG43" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AL43" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B44" s="4">
         <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D44" s="4">
         <v>4</v>
@@ -5440,7 +5500,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J44" s="4">
         <v>0</v>
@@ -5458,16 +5518,16 @@
         <v>0</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
@@ -5478,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC44" s="4">
         <v>30</v>
@@ -5487,31 +5547,31 @@
         <v>3</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AF44" s="4">
         <v>1</v>
       </c>
       <c r="AG44" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK44" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AL44" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5528,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J45" s="4">
         <v>0</v>
@@ -5546,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
@@ -5566,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC45" s="4">
         <v>30</v>
@@ -5575,33 +5635,33 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AF45" s="4">
         <v>1</v>
       </c>
       <c r="AG45" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK45" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B46" s="4">
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5613,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J46" s="4">
         <v>0</v>
@@ -5631,22 +5691,22 @@
         <v>0</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5657,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC46" s="4">
         <v>30</v>
@@ -5666,28 +5726,28 @@
         <v>0</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AF46" s="4">
         <v>1</v>
       </c>
       <c r="AG46" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK46" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="47" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5704,7 +5764,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J47" s="4">
         <v>0</v>
@@ -5722,19 +5782,19 @@
         <v>0</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -5745,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC47" s="4">
         <v>30</v>
@@ -5754,28 +5814,28 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AF47" s="4">
         <v>1</v>
       </c>
       <c r="AG47" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK47" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5792,7 +5852,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J48" s="4">
         <v>0</v>
@@ -5810,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
@@ -5830,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC48" s="4">
         <v>30</v>
@@ -5839,28 +5899,28 @@
         <v>3</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AF48" s="4">
         <v>1</v>
       </c>
       <c r="AG48" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK48" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="49" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -5877,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J49" s="4">
         <v>0</v>
@@ -5895,16 +5955,16 @@
         <v>0</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
@@ -5915,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC49" s="4">
         <v>30</v>
@@ -5924,33 +5984,33 @@
         <v>2</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AF49" s="4">
         <v>1</v>
       </c>
       <c r="AG49" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK49" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="50" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="50" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B50" s="4">
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D50" s="4">
         <v>4</v>
@@ -5962,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J50" s="4">
         <v>0</v>
@@ -5980,19 +6040,19 @@
         <v>0</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -6003,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC50" s="4">
         <v>30</v>
@@ -6012,28 +6072,28 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AF50" s="4">
         <v>1</v>
       </c>
       <c r="AG50" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK50" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="51" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -6050,7 +6110,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J51" s="4">
         <v>0</v>
@@ -6068,17 +6128,17 @@
         <v>0</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S51" s="4"/>
       <c r="T51" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W51" s="4">
         <v>240</v>
@@ -6091,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="AB51" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC51" s="4">
         <v>30</v>
@@ -6100,28 +6160,28 @@
         <v>3</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AF51" s="4">
         <v>3</v>
       </c>
       <c r="AG51" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK51" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -6138,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J52" s="4">
         <v>0</v>
@@ -6156,17 +6216,17 @@
         <v>0</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S52" s="4"/>
       <c r="T52" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W52" s="4">
         <v>180</v>
@@ -6179,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC52" s="4">
         <v>30</v>
@@ -6188,28 +6248,28 @@
         <v>3</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AF52" s="4">
         <v>2</v>
       </c>
       <c r="AG52" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK52" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="53" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -6226,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J53" s="4">
         <v>0</v>
@@ -6244,14 +6304,14 @@
         <v>0</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S53" s="4"/>
       <c r="T53" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W53" s="4">
         <v>60</v>
@@ -6264,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="AB53" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC53" s="4">
         <v>0</v>
@@ -6273,24 +6333,24 @@
         <v>3</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="4"/>
       <c r="AH53" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK53" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="54" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -6307,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J54" s="4">
         <v>0</v>
@@ -6325,17 +6385,17 @@
         <v>0</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S54" s="4"/>
       <c r="T54" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W54" s="4"/>
       <c r="X54" s="4">
@@ -6348,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="AB54" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC54" s="4">
         <v>30</v>
@@ -6357,31 +6417,31 @@
         <v>0</v>
       </c>
       <c r="AE54" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AF54" s="4">
         <v>1</v>
       </c>
       <c r="AG54" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK54" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AL54" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="55" spans="2:38" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6395,13 +6455,13 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H55" s="4">
         <v>2</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J55" s="4">
         <v>0</v>
@@ -6419,14 +6479,14 @@
         <v>0</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S55" s="4"/>
       <c r="T55" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W55" s="4">
         <v>90</v>
@@ -6439,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC55" s="4">
         <v>20</v>
@@ -6448,24 +6508,24 @@
         <v>3</v>
       </c>
       <c r="AE55" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="4"/>
       <c r="AH55" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK55" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="56" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="56" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6482,7 +6542,7 @@
         <v>3</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J56" s="4">
         <v>0</v>
@@ -6500,14 +6560,14 @@
         <v>0</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S56" s="4"/>
       <c r="T56" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W56" s="4">
         <v>120</v>
@@ -6520,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="AB56" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC56" s="4">
         <v>20</v>
@@ -6529,24 +6589,24 @@
         <v>3</v>
       </c>
       <c r="AE56" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="4"/>
       <c r="AH56" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK56" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="57" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6560,13 +6620,13 @@
         <v>33</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H57" s="4">
         <v>2</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J57" s="4">
         <v>0</v>
@@ -6584,14 +6644,14 @@
         <v>0</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S57" s="4"/>
       <c r="T57" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W57" s="4"/>
       <c r="X57" s="4">
@@ -6604,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC57" s="4">
         <v>20</v>
@@ -6613,24 +6673,24 @@
         <v>3</v>
       </c>
       <c r="AE57" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="4"/>
       <c r="AH57" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK57" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="58" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6647,7 +6707,7 @@
         <v>3</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J58" s="4">
         <v>0</v>
@@ -6665,14 +6725,14 @@
         <v>0</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="S58" s="4"/>
       <c r="T58" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W58" s="4"/>
       <c r="X58" s="4">
@@ -6685,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC58" s="4">
         <v>20</v>
@@ -6694,24 +6754,24 @@
         <v>3</v>
       </c>
       <c r="AE58" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="4"/>
       <c r="AH58" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK58" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="59" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6725,13 +6785,13 @@
         <v>34</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H59" s="4">
         <v>2</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J59" s="4">
         <v>0</v>
@@ -6749,22 +6809,22 @@
         <v>0</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S59" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="T59" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="T59" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="U59" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6775,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC59" s="4">
         <v>20</v>
@@ -6784,24 +6844,24 @@
         <v>4</v>
       </c>
       <c r="AE59" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="4"/>
       <c r="AH59" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK59" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="60" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="60" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6818,7 +6878,7 @@
         <v>3</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J60" s="4">
         <v>0</v>
@@ -6836,22 +6896,22 @@
         <v>0</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6862,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC60" s="4">
         <v>20</v>
@@ -6871,24 +6931,24 @@
         <v>4</v>
       </c>
       <c r="AE60" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="4"/>
       <c r="AH60" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK60" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="61" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -6902,13 +6962,13 @@
         <v>35</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H61" s="4">
         <v>2</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J61" s="4">
         <v>0</v>
@@ -6926,22 +6986,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6952,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC61" s="4">
         <v>20</v>
@@ -6961,24 +7021,24 @@
         <v>2</v>
       </c>
       <c r="AE61" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="4"/>
       <c r="AH61" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AI61" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="AJ61" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="AK61" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="62" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -6995,7 +7055,7 @@
         <v>3</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J62" s="4">
         <v>0</v>
@@ -7013,22 +7073,22 @@
         <v>0</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -7039,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="AB62" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC62" s="4">
         <v>20</v>
@@ -7048,24 +7108,24 @@
         <v>2</v>
       </c>
       <c r="AE62" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="4"/>
       <c r="AH62" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AI62" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ62" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="AJ62" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="AK62" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -7085,7 +7145,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J63" s="4">
         <v>0</v>
@@ -7103,22 +7163,22 @@
         <v>0</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -7130,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="AB63" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC63" s="4">
         <v>20</v>
@@ -7139,24 +7199,24 @@
         <v>2</v>
       </c>
       <c r="AE63" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="4"/>
       <c r="AH63" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AI63" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AJ63" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK63" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="2:38" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="64" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -7174,7 +7234,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J64" s="4">
         <v>0</v>
@@ -7192,22 +7252,22 @@
         <v>0</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -7219,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="AB64" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC64" s="4">
         <v>20</v>
@@ -7228,29 +7288,29 @@
         <v>2</v>
       </c>
       <c r="AE64" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="4"/>
       <c r="AH64" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AI64" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AJ64" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK64" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="65" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B65" s="4">
         <v>61</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D65" s="4">
         <v>4</v>
@@ -7259,13 +7319,13 @@
         <v>37</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H65" s="4">
         <v>2</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J65" s="4">
         <v>0</v>
@@ -7283,22 +7343,22 @@
         <v>0</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -7309,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AB65" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC65" s="4">
         <v>30</v>
@@ -7318,29 +7378,29 @@
         <v>2</v>
       </c>
       <c r="AE65" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF65" s="4"/>
       <c r="AG65" s="4"/>
       <c r="AH65" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK65" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B66" s="4">
         <v>62</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D66" s="4">
         <v>4</v>
@@ -7352,7 +7412,7 @@
         <v>3</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J66" s="4">
         <v>0</v>
@@ -7370,22 +7430,22 @@
         <v>0</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7396,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AB66" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC66" s="4">
         <v>30</v>
@@ -7405,29 +7465,29 @@
         <v>2</v>
       </c>
       <c r="AE66" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF66" s="4"/>
       <c r="AG66" s="4"/>
       <c r="AH66" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AJ66" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK66" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="67" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B67" s="4">
         <v>63</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D67" s="4">
         <v>4</v>
@@ -7436,13 +7496,13 @@
         <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H67" s="4">
         <v>2</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J67" s="4">
         <v>0</v>
@@ -7460,22 +7520,22 @@
         <v>0</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7486,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="AB67" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC67" s="4">
         <v>30</v>
@@ -7495,29 +7555,29 @@
         <v>2</v>
       </c>
       <c r="AE67" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF67" s="4"/>
       <c r="AG67" s="4"/>
       <c r="AH67" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK67" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="68" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B68" s="4">
         <v>64</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D68" s="4">
         <v>4</v>
@@ -7529,7 +7589,7 @@
         <v>3</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J68" s="4">
         <v>0</v>
@@ -7547,22 +7607,22 @@
         <v>0</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7573,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC68" s="4">
         <v>30</v>
@@ -7582,24 +7642,24 @@
         <v>2</v>
       </c>
       <c r="AE68" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF68" s="4"/>
       <c r="AG68" s="4"/>
       <c r="AH68" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AJ68" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK68" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="69" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7616,7 +7676,7 @@
       <c r="AF69" s="4"/>
       <c r="AG69" s="4"/>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7642,7 +7702,7 @@
       <c r="AG70" s="4"/>
       <c r="AN70" s="4"/>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7665,7 +7725,7 @@
       <c r="AG71" s="4"/>
       <c r="AN71" s="4"/>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7688,7 +7748,7 @@
       <c r="AG72" s="4"/>
       <c r="AN72" s="4"/>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7711,7 +7771,7 @@
       <c r="AG73" s="4"/>
       <c r="AN73" s="4"/>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7734,7 +7794,7 @@
       <c r="AG74" s="4"/>
       <c r="AN74" s="4"/>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7757,7 +7817,7 @@
       <c r="AG75" s="4"/>
       <c r="AN75" s="4"/>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7780,7 +7840,7 @@
       <c r="AG76" s="4"/>
       <c r="AN76" s="4"/>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7803,7 +7863,7 @@
       <c r="AG77" s="4"/>
       <c r="AN77" s="4"/>
     </row>
-    <row r="78" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7826,7 +7886,7 @@
       <c r="AG78" s="4"/>
       <c r="AN78" s="4"/>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7849,7 +7909,7 @@
       <c r="AG79" s="4"/>
       <c r="AN79" s="4"/>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7872,7 +7932,7 @@
       <c r="AG80" s="4"/>
       <c r="AN80" s="4"/>
     </row>
-    <row r="81" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7895,7 +7955,7 @@
       <c r="AG81" s="4"/>
       <c r="AN81" s="4"/>
     </row>
-    <row r="82" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7918,7 +7978,7 @@
       <c r="AG82" s="4"/>
       <c r="AN82" s="4"/>
     </row>
-    <row r="83" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7941,7 +8001,7 @@
       <c r="AG83" s="4"/>
       <c r="AN83" s="4"/>
     </row>
-    <row r="84" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -7964,7 +8024,7 @@
       <c r="AG84" s="4"/>
       <c r="AN84" s="4"/>
     </row>
-    <row r="85" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -7987,7 +8047,7 @@
       <c r="AG85" s="4"/>
       <c r="AN85" s="4"/>
     </row>
-    <row r="86" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -8010,7 +8070,7 @@
       <c r="AG86" s="4"/>
       <c r="AN86" s="4"/>
     </row>
-    <row r="87" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -8033,7 +8093,7 @@
       <c r="AG87" s="4"/>
       <c r="AN87" s="4"/>
     </row>
-    <row r="88" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -8056,7 +8116,7 @@
       <c r="AG88" s="4"/>
       <c r="AN88" s="4"/>
     </row>
-    <row r="89" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -8079,7 +8139,7 @@
       <c r="AG89" s="4"/>
       <c r="AN89" s="4"/>
     </row>
-    <row r="90" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8102,7 +8162,7 @@
       <c r="AG90" s="4"/>
       <c r="AN90" s="4"/>
     </row>
-    <row r="91" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -8125,7 +8185,7 @@
       <c r="AG91" s="4"/>
       <c r="AN91" s="4"/>
     </row>
-    <row r="92" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -8148,7 +8208,7 @@
       <c r="AG92" s="4"/>
       <c r="AN92" s="4"/>
     </row>
-    <row r="93" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -8162,7 +8222,7 @@
       <c r="AG93" s="4"/>
       <c r="AN93" s="4"/>
     </row>
-    <row r="94" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -8182,7 +8242,7 @@
       <c r="AG94" s="4"/>
       <c r="AN94" s="4"/>
     </row>
-    <row r="95" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -8202,7 +8262,7 @@
       <c r="AG95" s="4"/>
       <c r="AN95" s="4"/>
     </row>
-    <row r="96" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -8222,7 +8282,7 @@
       <c r="AG96" s="4"/>
       <c r="AN96" s="4"/>
     </row>
-    <row r="97" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -8242,7 +8302,7 @@
       <c r="AG97" s="4"/>
       <c r="AN97" s="4"/>
     </row>
-    <row r="98" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -8262,7 +8322,7 @@
       <c r="AG98" s="4"/>
       <c r="AN98" s="4"/>
     </row>
-    <row r="99" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -8282,7 +8342,7 @@
       <c r="AG99" s="4"/>
       <c r="AN99" s="4"/>
     </row>
-    <row r="100" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -8302,7 +8362,7 @@
       <c r="AG100" s="4"/>
       <c r="AN100" s="4"/>
     </row>
-    <row r="101" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -8322,7 +8382,7 @@
       <c r="AG101" s="4"/>
       <c r="AN101" s="4"/>
     </row>
-    <row r="102" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -8342,7 +8402,7 @@
       <c r="AG102" s="4"/>
       <c r="AN102" s="4"/>
     </row>
-    <row r="103" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -8354,7 +8414,7 @@
       <c r="AF103" s="4"/>
       <c r="AG103" s="4"/>
     </row>
-    <row r="104" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -8366,7 +8426,7 @@
       <c r="AF104" s="4"/>
       <c r="AG104" s="4"/>
     </row>
-    <row r="105" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -8378,7 +8438,7 @@
       <c r="AF105" s="4"/>
       <c r="AG105" s="4"/>
     </row>
-    <row r="106" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -8390,7 +8450,7 @@
       <c r="AF106" s="4"/>
       <c r="AG106" s="4"/>
     </row>
-    <row r="107" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -8402,7 +8462,7 @@
       <c r="AF107" s="4"/>
       <c r="AG107" s="4"/>
     </row>
-    <row r="108" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8414,7 +8474,7 @@
       <c r="AF108" s="4"/>
       <c r="AG108" s="4"/>
     </row>
-    <row r="109" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8426,7 +8486,7 @@
       <c r="AF109" s="4"/>
       <c r="AG109" s="4"/>
     </row>
-    <row r="110" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8438,7 +8498,7 @@
       <c r="AF110" s="4"/>
       <c r="AG110" s="4"/>
     </row>
-    <row r="111" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8450,7 +8510,7 @@
       <c r="AF111" s="4"/>
       <c r="AG111" s="4"/>
     </row>
-    <row r="112" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8462,7 +8522,7 @@
       <c r="AF112" s="4"/>
       <c r="AG112" s="4"/>
     </row>
-    <row r="113" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8474,7 +8534,7 @@
       <c r="AF113" s="4"/>
       <c r="AG113" s="4"/>
     </row>
-    <row r="114" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8486,7 +8546,7 @@
       <c r="AF114" s="4"/>
       <c r="AG114" s="4"/>
     </row>
-    <row r="115" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8498,7 +8558,7 @@
       <c r="AF115" s="4"/>
       <c r="AG115" s="4"/>
     </row>
-    <row r="116" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8510,7 +8570,7 @@
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
     </row>
-    <row r="117" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8522,7 +8582,7 @@
       <c r="AF117" s="4"/>
       <c r="AG117" s="4"/>
     </row>
-    <row r="118" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8534,7 +8594,7 @@
       <c r="AF118" s="4"/>
       <c r="AG118" s="4"/>
     </row>
-    <row r="119" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8546,7 +8606,7 @@
       <c r="AF119" s="4"/>
       <c r="AG119" s="4"/>
     </row>
-    <row r="120" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7872FED-0AB0-48E7-B4E7-DCBC4EB86D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853968F-FA2C-4140-B8F3-EF869ADD0FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="2805" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="342">
   <si>
     <t>0</t>
   </si>
@@ -912,10 +912,6 @@
   </si>
   <si>
     <t>11,12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1870,19 +1866,19 @@
         <v>233</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>232</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>102</v>
@@ -1906,7 +1902,7 @@
         <v>159</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
@@ -2028,25 +2024,25 @@
         <v>234</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="S3" s="8" t="s">
         <v>231</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>235</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>109</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>114</v>
@@ -2070,7 +2066,7 @@
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG3" s="8" t="s">
         <v>153</v>
@@ -2162,10 +2158,10 @@
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2240,10 +2236,10 @@
         <v>123</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>120</v>
@@ -2318,10 +2314,10 @@
         <v>124</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>122</v>
@@ -2395,10 +2391,10 @@
         <v>124</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>121</v>
@@ -2450,7 +2446,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2518,19 +2514,19 @@
       <c r="AF8" s="4"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AI8" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="AJ8" s="2" t="s">
+      <c r="AK8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AK8" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="AL8" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AN8" s="4"/>
     </row>
@@ -2539,7 +2535,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2607,19 +2603,19 @@
       <c r="AF9" s="4"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AJ9" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="AK9" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AK9" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="AL9" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AN9" s="4"/>
     </row>
@@ -2696,19 +2692,19 @@
       <c r="AF10" s="4"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AJ10" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="AK10" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AK10" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="AL10" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AN10" s="4"/>
     </row>
@@ -2785,7 +2781,7 @@
       <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AI11" s="2" t="s">
         <v>184</v>
@@ -2871,10 +2867,10 @@
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AJ12" s="2" t="s">
         <v>211</v>
@@ -2953,16 +2949,16 @@
       <c r="AF13" s="4"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AI13" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="AJ13" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="AK13" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN13" s="4"/>
     </row>
@@ -3030,21 +3026,21 @@
       </c>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AI14" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="AJ14" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="AK14" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AN14" s="4"/>
     </row>
@@ -3121,16 +3117,16 @@
       <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AI15" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="AJ15" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="AK15" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN15" s="4"/>
     </row>
@@ -3202,24 +3198,24 @@
         <v>3</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AI16" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="AJ16" s="2" t="s">
+      <c r="AK16" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="AK16" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="AL16" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AN16" s="4"/>
     </row>
@@ -3296,19 +3292,19 @@
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AI17" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="AJ17" s="2" t="s">
+      <c r="AK17" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AK17" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="AL17" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AN17" s="4"/>
     </row>
@@ -3385,7 +3381,7 @@
       <c r="AF18" s="4"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AI18" s="2" t="s">
         <v>128</v>
@@ -3394,7 +3390,7 @@
         <v>210</v>
       </c>
       <c r="AK18" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN18" s="4"/>
     </row>
@@ -3472,7 +3468,7 @@
         <v>210</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN19" s="4"/>
     </row>
@@ -3550,7 +3546,7 @@
         <v>210</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN20" s="4"/>
     </row>
@@ -3623,16 +3619,16 @@
       <c r="AF21" s="4"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN21" s="4"/>
     </row>
@@ -3705,16 +3701,16 @@
       <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN22" s="4"/>
     </row>
@@ -3787,16 +3783,16 @@
       <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK23" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN23" s="4"/>
     </row>
@@ -3869,16 +3865,16 @@
       <c r="AF24" s="4"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN24" s="4"/>
     </row>
@@ -3951,16 +3947,16 @@
       <c r="AF25" s="4"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN25" s="4"/>
     </row>
@@ -4033,16 +4029,16 @@
       <c r="AF26" s="4"/>
       <c r="AG26" s="4"/>
       <c r="AH26" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN26" s="4"/>
     </row>
@@ -4115,16 +4111,16 @@
       <c r="AF27" s="4"/>
       <c r="AG27" s="4"/>
       <c r="AH27" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK27" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN27" s="4"/>
     </row>
@@ -4196,13 +4192,13 @@
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
       <c r="AI28" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN28" s="4"/>
     </row>
@@ -4274,13 +4270,13 @@
       <c r="AG29" s="4"/>
       <c r="AH29" s="4"/>
       <c r="AI29" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN29" s="4"/>
     </row>
@@ -4350,13 +4346,13 @@
       <c r="AG30" s="4"/>
       <c r="AH30" s="4"/>
       <c r="AI30" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK30" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN30" s="4"/>
     </row>
@@ -4428,13 +4424,13 @@
       <c r="AG31" s="4"/>
       <c r="AH31" s="4"/>
       <c r="AI31" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN31" s="4"/>
     </row>
@@ -4504,13 +4500,13 @@
       <c r="AG32" s="4"/>
       <c r="AH32" s="4"/>
       <c r="AI32" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK32" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN32" s="4"/>
     </row>
@@ -4582,13 +4578,13 @@
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
       <c r="AI33" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK33" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN33" s="4"/>
     </row>
@@ -4660,13 +4656,13 @@
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>
       <c r="AI34" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK34" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN34" s="4"/>
     </row>
@@ -4741,16 +4737,16 @@
         <v>155</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK35" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AN35" s="4"/>
     </row>
@@ -4833,7 +4829,7 @@
         <v>183</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AI36" s="2" t="s">
         <v>185</v>
@@ -4925,7 +4921,7 @@
         <v>183</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI37" s="2" t="s">
         <v>186</v>
@@ -4982,13 +4978,13 @@
         <v>136</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -5015,7 +5011,7 @@
         <v>183</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>187</v>
@@ -5071,16 +5067,16 @@
         <v>136</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>237</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -5107,7 +5103,7 @@
         <v>183</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AI39" s="2" t="s">
         <v>188</v>
@@ -5163,16 +5159,16 @@
         <v>136</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>238</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -5199,7 +5195,7 @@
         <v>183</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AI40" s="2" t="s">
         <v>189</v>
@@ -5255,16 +5251,16 @@
         <v>136</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>239</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -5291,7 +5287,7 @@
         <v>183</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AI41" s="2" t="s">
         <v>190</v>
@@ -5347,16 +5343,16 @@
         <v>136</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5383,7 +5379,7 @@
         <v>183</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AI42" s="2" t="s">
         <v>191</v>
@@ -5468,7 +5464,7 @@
         <v>156</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AI43" s="2" t="s">
         <v>192</v>
@@ -5556,7 +5552,7 @@
         <v>156</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AI44" s="2" t="s">
         <v>193</v>
@@ -5635,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AF45" s="4">
         <v>1</v>
@@ -5644,7 +5640,7 @@
         <v>156</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AI45" s="2" t="s">
         <v>194</v>
@@ -5661,7 +5657,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5706,7 +5702,7 @@
         <v>136</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5726,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF46" s="4">
         <v>1</v>
@@ -5735,7 +5731,7 @@
         <v>156</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AI46" s="2" t="s">
         <v>195</v>
@@ -5814,7 +5810,7 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AF47" s="4">
         <v>1</v>
@@ -5823,7 +5819,7 @@
         <v>156</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AI47" s="2" t="s">
         <v>196</v>
@@ -5908,7 +5904,7 @@
         <v>156</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AI48" s="2" t="s">
         <v>197</v>
@@ -5993,7 +5989,7 @@
         <v>156</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AI49" s="2" t="s">
         <v>198</v>
@@ -6052,7 +6048,7 @@
         <v>136</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -6072,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AF50" s="4">
         <v>1</v>
@@ -6081,7 +6077,7 @@
         <v>156</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AI50" s="2" t="s">
         <v>199</v>
@@ -6169,7 +6165,7 @@
         <v>157</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AI51" s="2" t="s">
         <v>200</v>
@@ -6257,10 +6253,10 @@
         <v>158</v>
       </c>
       <c r="AH52" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI52" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="AI52" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="AJ52" s="2" t="s">
         <v>208</v>
@@ -6338,7 +6334,7 @@
       <c r="AF53" s="4"/>
       <c r="AG53" s="4"/>
       <c r="AH53" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AI53" s="2" t="s">
         <v>201</v>
@@ -6426,7 +6422,7 @@
         <v>156</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AI54" s="2" t="s">
         <v>202</v>
@@ -6513,7 +6509,7 @@
       <c r="AF55" s="4"/>
       <c r="AG55" s="4"/>
       <c r="AH55" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AI55" s="2" t="s">
         <v>203</v>
@@ -6594,7 +6590,7 @@
       <c r="AF56" s="4"/>
       <c r="AG56" s="4"/>
       <c r="AH56" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AI56" s="2" t="s">
         <v>203</v>
@@ -6678,7 +6674,7 @@
       <c r="AF57" s="4"/>
       <c r="AG57" s="4"/>
       <c r="AH57" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI57" s="2" t="s">
         <v>204</v>
@@ -6759,7 +6755,7 @@
       <c r="AF58" s="4"/>
       <c r="AG58" s="4"/>
       <c r="AH58" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI58" s="2" t="s">
         <v>204</v>
@@ -6815,16 +6811,13 @@
         <v>136</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6849,7 +6842,7 @@
       <c r="AF59" s="4"/>
       <c r="AG59" s="4"/>
       <c r="AH59" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI59" s="2" t="s">
         <v>205</v>
@@ -6902,16 +6895,13 @@
         <v>136</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="U60" s="2" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6936,7 +6926,7 @@
       <c r="AF60" s="4"/>
       <c r="AG60" s="4"/>
       <c r="AH60" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI60" s="2" t="s">
         <v>205</v>
@@ -6992,16 +6982,16 @@
         <v>136</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U61" s="2" t="s">
         <v>237</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -7026,7 +7016,7 @@
       <c r="AF61" s="4"/>
       <c r="AG61" s="4"/>
       <c r="AH61" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AI61" s="2" t="s">
         <v>206</v>
@@ -7079,16 +7069,16 @@
         <v>136</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U62" s="2" t="s">
         <v>237</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -7113,7 +7103,7 @@
       <c r="AF62" s="4"/>
       <c r="AG62" s="4"/>
       <c r="AH62" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AI62" s="2" t="s">
         <v>206</v>
@@ -7169,16 +7159,16 @@
         <v>136</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U63" s="2" t="s">
         <v>238</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -7204,7 +7194,7 @@
       <c r="AF63" s="4"/>
       <c r="AG63" s="4"/>
       <c r="AH63" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AI63" s="2" t="s">
         <v>207</v>
@@ -7258,16 +7248,16 @@
         <v>136</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>238</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -7293,7 +7283,7 @@
       <c r="AF64" s="4"/>
       <c r="AG64" s="4"/>
       <c r="AH64" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AI64" s="2" t="s">
         <v>207</v>
@@ -7352,13 +7342,13 @@
         <v>132</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>239</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -7383,7 +7373,7 @@
       <c r="AF65" s="4"/>
       <c r="AG65" s="4"/>
       <c r="AH65" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AI65" s="2" t="s">
         <v>190</v>
@@ -7439,13 +7429,13 @@
         <v>124</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="U66" s="2" t="s">
         <v>239</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7470,7 +7460,7 @@
       <c r="AF66" s="4"/>
       <c r="AG66" s="4"/>
       <c r="AH66" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AI66" s="2" t="s">
         <v>190</v>
@@ -7529,13 +7519,13 @@
         <v>132</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="U67" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7560,7 +7550,7 @@
       <c r="AF67" s="4"/>
       <c r="AG67" s="4"/>
       <c r="AH67" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AI67" s="2" t="s">
         <v>191</v>
@@ -7616,13 +7606,13 @@
         <v>124</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>240</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7647,7 +7637,7 @@
       <c r="AF68" s="4"/>
       <c r="AG68" s="4"/>
       <c r="AH68" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AI68" s="2" t="s">
         <v>191</v>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853968F-FA2C-4140-B8F3-EF869ADD0FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9AE523-3C2B-43DF-8E9B-F58E57721D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -2541,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4"/>
       <c r="H9" s="4">
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4"/>
       <c r="H10" s="4">
@@ -2805,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="4"/>
       <c r="H12" s="4">
@@ -2973,7 +2973,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4"/>
       <c r="H14" s="4">
